--- a/data/positions/Posição Consolidada - 7983962.xlsx
+++ b/data/positions/Posição Consolidada - 7983962.xlsx
@@ -19,7 +19,7 @@
     <x:t>XP</x:t>
   </x:si>
   <x:si>
-    <x:t>Conta: 7983962 | 21/08/2026, 14:52</x:t>
+    <x:t>Conta: 7983962 | 25/08/2026, 19:24</x:t>
   </x:si>
   <x:si>
     <x:t>Este é o seu patrimônio</x:t>
@@ -37,7 +37,7 @@
     <x:t>19,7%|Renda Fixa</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 1.031.234,13</x:t>
+    <x:t>R$ 1.032.134,65</x:t>
   </x:si>
   <x:si>
     <x:t>19,60%|Pós-Fixada</x:t>
@@ -97,7 +97,7 @@
     <x:t>46,0%|Operações Compromissadas</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 2.409.230,05</x:t>
+    <x:t>R$ 2.411.346,34</x:t>
   </x:si>
   <x:si>
     <x:t>45,90%|Pós-Fixada</x:t>
@@ -118,10 +118,10 @@
     <x:t>R$ 1.603.779,99</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 1.606.598,79</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 1.605.964,56</x:t>
+    <x:t>R$ 1.608.010,04</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 1.607.058,28</x:t>
   </x:si>
   <x:si>
     <x:t>510.333,00</x:t>
@@ -130,16 +130,16 @@
     <x:t>R$ 801.223,03</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 802.631,26</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 802.314,41</x:t>
+    <x:t>R$ 803.336,30</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 802.860,81</x:t>
   </x:si>
   <x:si>
     <x:t>34,3%|Fundos de Investimento</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 1.798.796,29</x:t>
+    <x:t>R$ 1.800.619,22</x:t>
   </x:si>
   <x:si>
     <x:t>34,30%|Fundos de Renda Fixa Pós-Fixado</x:t>
@@ -160,10 +160,10 @@
     <x:t>Bradesco SKY FIC FIRF Referenciada DI RL</x:t>
   </x:si>
   <x:si>
-    <x:t>21/08/2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 1.439,63</x:t>
+    <x:t>25/08/2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 1.441,09</x:t>
   </x:si>
   <x:si>
     <x:t>15,17</x:t>
@@ -172,10 +172,10 @@
     <x:t>R$ 0,00</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 21.838,76</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 21.731,50</x:t>
+    <x:t>R$ 21.861,02</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 21.748,75</x:t>
   </x:si>
   <x:si>
     <x:t>Bradesco Bancos II FIF CIC RF CP RL</x:t>
@@ -187,25 +187,25 @@
     <x:t>353.356,60</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 519.633,42</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 515.411,60</x:t>
+    <x:t>R$ 520.186,85</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 515.840,51</x:t>
   </x:si>
   <x:si>
     <x:t>Safra Extra Bancos Special FIC FIRF CP</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 141,30</x:t>
+    <x:t>R$ 141,44</x:t>
   </x:si>
   <x:si>
     <x:t>8.898,52</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 1.257.324,11</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 1.250.770,71</x:t>
+    <x:t>R$ 1.258.571,35</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 1.251.737,32</x:t>
   </x:si>
   <x:si>
     <x:t>R$ 2,20</x:t>
@@ -846,10 +846,10 @@
     </x:row>
     <x:row r="4" spans="1:11" ht="30" customHeight="1">
       <x:c r="A4" s="6">
-        <x:v>5239262.66420238</x:v>
+        <x:v>5244102.40860837</x:v>
       </x:c>
       <x:c r="B4" s="7">
-        <x:v>5239260.46420238</x:v>
+        <x:v>5244100.20860837</x:v>
       </x:c>
       <x:c r="C4" s="7">
         <x:v>2.2</x:v>

--- a/data/positions/Posição Consolidada - 7983962.xlsx
+++ b/data/positions/Posição Consolidada - 7983962.xlsx
@@ -19,7 +19,7 @@
     <x:t>XP</x:t>
   </x:si>
   <x:si>
-    <x:t>Conta: 7983962 | 25/08/2026, 19:24</x:t>
+    <x:t>Conta: 7983962 | 28/08/2026, 09:34</x:t>
   </x:si>
   <x:si>
     <x:t>Este é o seu patrimônio</x:t>
@@ -37,7 +37,7 @@
     <x:t>19,7%|Renda Fixa</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 1.032.134,65</x:t>
+    <x:t>R$ 1.033.486,90</x:t>
   </x:si>
   <x:si>
     <x:t>19,60%|Pós-Fixada</x:t>
@@ -97,7 +97,7 @@
     <x:t>46,0%|Operações Compromissadas</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 2.411.346,34</x:t>
+    <x:t>R$ 2.414.524,27</x:t>
   </x:si>
   <x:si>
     <x:t>45,90%|Pós-Fixada</x:t>
@@ -118,10 +118,10 @@
     <x:t>R$ 1.603.779,99</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 1.608.010,04</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 1.607.058,28</x:t>
+    <x:t>R$ 1.610.129,25</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 1.608.700,67</x:t>
   </x:si>
   <x:si>
     <x:t>510.333,00</x:t>
@@ -130,16 +130,16 @@
     <x:t>R$ 801.223,03</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 803.336,30</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 802.860,81</x:t>
+    <x:t>R$ 804.395,02</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 803.681,32</x:t>
   </x:si>
   <x:si>
     <x:t>34,3%|Fundos de Investimento</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 1.800.619,22</x:t>
+    <x:t>R$ 1.802.730,16</x:t>
   </x:si>
   <x:si>
     <x:t>34,30%|Fundos de Renda Fixa Pós-Fixado</x:t>
@@ -160,10 +160,10 @@
     <x:t>Bradesco SKY FIC FIRF Referenciada DI RL</x:t>
   </x:si>
   <x:si>
-    <x:t>25/08/2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 1.441,09</x:t>
+    <x:t>28/08/2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 1.443,31</x:t>
   </x:si>
   <x:si>
     <x:t>15,17</x:t>
@@ -172,10 +172,10 @@
     <x:t>R$ 0,00</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 21.861,02</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 21.748,75</x:t>
+    <x:t>R$ 21.894,69</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 21.774,84</x:t>
   </x:si>
   <x:si>
     <x:t>Bradesco Bancos II FIF CIC RF CP RL</x:t>
@@ -187,25 +187,28 @@
     <x:t>353.356,60</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 520.186,85</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 515.840,51</x:t>
+    <x:t>R$ 521.009,75</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 516.478,26</x:t>
   </x:si>
   <x:si>
     <x:t>Safra Extra Bancos Special FIC FIRF CP</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 141,44</x:t>
+    <x:t>27/08/2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 141,58</x:t>
   </x:si>
   <x:si>
     <x:t>8.898,52</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 1.258.571,35</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 1.251.737,32</x:t>
+    <x:t>R$ 1.259.825,72</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 1.252.709,46</x:t>
   </x:si>
   <x:si>
     <x:t>R$ 2,20</x:t>
@@ -846,10 +849,10 @@
     </x:row>
     <x:row r="4" spans="1:11" ht="30" customHeight="1">
       <x:c r="A4" s="6">
-        <x:v>5244102.40860837</x:v>
+        <x:v>5250743.53542968</x:v>
       </x:c>
       <x:c r="B4" s="7">
-        <x:v>5244100.20860837</x:v>
+        <x:v>5250741.33542968</x:v>
       </x:c>
       <x:c r="C4" s="7">
         <x:v>2.2</x:v>
@@ -1250,22 +1253,22 @@
         <x:v>59</x:v>
       </x:c>
       <x:c r="B23" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="C23" s="12" t="s">
-        <x:v>60</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="D23" s="12" t="s">
-        <x:v>61</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="E23" s="12" t="s">
         <x:v>51</x:v>
       </x:c>
       <x:c r="F23" s="12" t="s">
-        <x:v>62</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="G23" s="12" t="s">
-        <x:v>63</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="H23" s="3"/>
       <x:c r="I23" s="3"/>
@@ -1299,7 +1302,7 @@
       <x:c r="I25" s="9"/>
       <x:c r="J25" s="9"/>
       <x:c r="K25" s="10" t="s">
-        <x:v>64</x:v>
+        <x:v>65</x:v>
       </x:c>
     </x:row>
     <x:row r="26" spans="1:11">
@@ -1323,66 +1326,66 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="C27" s="11" t="s">
-        <x:v>65</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="D27" s="11" t="s">
-        <x:v>66</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="E27" s="11" t="s">
-        <x:v>67</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="F27" s="11" t="s">
-        <x:v>68</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="G27" s="11" t="s">
-        <x:v>69</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="H27" s="11" t="s">
-        <x:v>70</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="I27" s="11" t="s">
-        <x:v>71</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="J27" s="11" t="s">
-        <x:v>72</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="K27" s="11" t="s">
-        <x:v>73</x:v>
+        <x:v>74</x:v>
       </x:c>
     </x:row>
     <x:row r="28" spans="1:11" ht="30" customHeight="1">
       <x:c r="A28" s="12" t="s">
-        <x:v>74</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="B28" s="12" t="s">
-        <x:v>75</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="C28" s="12" t="s">
-        <x:v>75</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="D28" s="12" t="s">
-        <x:v>75</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="E28" s="12" t="s">
-        <x:v>75</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="F28" s="12" t="s">
-        <x:v>75</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="G28" s="12" t="s">
-        <x:v>75</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="H28" s="12" t="s">
-        <x:v>75</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="I28" s="12" t="s">
-        <x:v>75</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="J28" s="12" t="s">
-        <x:v>75</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="K28" s="12" t="s">
-        <x:v>75</x:v>
+        <x:v>76</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/data/positions/Posição Consolidada - 7983962.xlsx
+++ b/data/positions/Posição Consolidada - 7983962.xlsx
@@ -19,7 +19,7 @@
     <x:t>XP</x:t>
   </x:si>
   <x:si>
-    <x:t>Conta: 7983962 | 28/08/2026, 09:34</x:t>
+    <x:t>Conta: 7983962 | 31/08/2026, 17:50</x:t>
   </x:si>
   <x:si>
     <x:t>Este é o seu patrimônio</x:t>
@@ -37,7 +37,7 @@
     <x:t>19,7%|Renda Fixa</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 1.033.486,90</x:t>
+    <x:t>R$ 1.033.938,05</x:t>
   </x:si>
   <x:si>
     <x:t>19,60%|Pós-Fixada</x:t>
@@ -97,7 +97,7 @@
     <x:t>46,0%|Operações Compromissadas</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 2.414.524,27</x:t>
+    <x:t>R$ 2.415.584,51</x:t>
   </x:si>
   <x:si>
     <x:t>45,90%|Pós-Fixada</x:t>
@@ -118,10 +118,10 @@
     <x:t>R$ 1.603.779,99</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 1.610.129,25</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 1.608.700,67</x:t>
+    <x:t>R$ 1.610.836,28</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 1.609.248,62</x:t>
   </x:si>
   <x:si>
     <x:t>510.333,00</x:t>
@@ -130,16 +130,16 @@
     <x:t>R$ 801.223,03</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 804.395,02</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 803.681,32</x:t>
+    <x:t>R$ 804.748,24</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 803.955,07</x:t>
   </x:si>
   <x:si>
     <x:t>34,3%|Fundos de Investimento</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 1.802.730,16</x:t>
+    <x:t>R$ 1.804.323,89</x:t>
   </x:si>
   <x:si>
     <x:t>34,30%|Fundos de Renda Fixa Pós-Fixado</x:t>
@@ -160,10 +160,10 @@
     <x:t>Bradesco SKY FIC FIRF Referenciada DI RL</x:t>
   </x:si>
   <x:si>
-    <x:t>28/08/2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 1.443,31</x:t>
+    <x:t>31/08/2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 1.444,03</x:t>
   </x:si>
   <x:si>
     <x:t>15,17</x:t>
@@ -172,43 +172,40 @@
     <x:t>R$ 0,00</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 21.894,69</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 21.774,84</x:t>
+    <x:t>R$ 21.905,59</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 21.783,29</x:t>
   </x:si>
   <x:si>
     <x:t>Bradesco Bancos II FIF CIC RF CP RL</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 1,47</x:t>
+    <x:t>R$ 1,48</x:t>
   </x:si>
   <x:si>
     <x:t>353.356,60</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 521.009,75</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 516.478,26</x:t>
+    <x:t>R$ 521.282,47</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 516.689,62</x:t>
   </x:si>
   <x:si>
     <x:t>Safra Extra Bancos Special FIC FIRF CP</x:t>
   </x:si>
   <x:si>
-    <x:t>27/08/2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 141,58</x:t>
+    <x:t>R$ 141,72</x:t>
   </x:si>
   <x:si>
     <x:t>8.898,52</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 1.259.825,72</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 1.252.709,46</x:t>
+    <x:t>R$ 1.261.135,83</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 1.253.724,79</x:t>
   </x:si>
   <x:si>
     <x:t>R$ 2,20</x:t>
@@ -849,10 +846,10 @@
     </x:row>
     <x:row r="4" spans="1:11" ht="30" customHeight="1">
       <x:c r="A4" s="6">
-        <x:v>5250743.53542968</x:v>
+        <x:v>5253848.65007597</x:v>
       </x:c>
       <x:c r="B4" s="7">
-        <x:v>5250741.33542968</x:v>
+        <x:v>5253846.45007597</x:v>
       </x:c>
       <x:c r="C4" s="7">
         <x:v>2.2</x:v>
@@ -1253,22 +1250,22 @@
         <x:v>59</x:v>
       </x:c>
       <x:c r="B23" s="12" t="s">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="C23" s="12" t="s">
         <x:v>60</x:v>
       </x:c>
-      <x:c r="C23" s="12" t="s">
+      <x:c r="D23" s="12" t="s">
         <x:v>61</x:v>
-      </x:c>
-      <x:c r="D23" s="12" t="s">
-        <x:v>62</x:v>
       </x:c>
       <x:c r="E23" s="12" t="s">
         <x:v>51</x:v>
       </x:c>
       <x:c r="F23" s="12" t="s">
+        <x:v>62</x:v>
+      </x:c>
+      <x:c r="G23" s="12" t="s">
         <x:v>63</x:v>
-      </x:c>
-      <x:c r="G23" s="12" t="s">
-        <x:v>64</x:v>
       </x:c>
       <x:c r="H23" s="3"/>
       <x:c r="I23" s="3"/>
@@ -1302,7 +1299,7 @@
       <x:c r="I25" s="9"/>
       <x:c r="J25" s="9"/>
       <x:c r="K25" s="10" t="s">
-        <x:v>65</x:v>
+        <x:v>64</x:v>
       </x:c>
     </x:row>
     <x:row r="26" spans="1:11">
@@ -1326,66 +1323,66 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="C27" s="11" t="s">
+        <x:v>65</x:v>
+      </x:c>
+      <x:c r="D27" s="11" t="s">
         <x:v>66</x:v>
       </x:c>
-      <x:c r="D27" s="11" t="s">
+      <x:c r="E27" s="11" t="s">
         <x:v>67</x:v>
       </x:c>
-      <x:c r="E27" s="11" t="s">
+      <x:c r="F27" s="11" t="s">
         <x:v>68</x:v>
       </x:c>
-      <x:c r="F27" s="11" t="s">
+      <x:c r="G27" s="11" t="s">
         <x:v>69</x:v>
       </x:c>
-      <x:c r="G27" s="11" t="s">
+      <x:c r="H27" s="11" t="s">
         <x:v>70</x:v>
       </x:c>
-      <x:c r="H27" s="11" t="s">
+      <x:c r="I27" s="11" t="s">
         <x:v>71</x:v>
       </x:c>
-      <x:c r="I27" s="11" t="s">
+      <x:c r="J27" s="11" t="s">
         <x:v>72</x:v>
       </x:c>
-      <x:c r="J27" s="11" t="s">
+      <x:c r="K27" s="11" t="s">
         <x:v>73</x:v>
-      </x:c>
-      <x:c r="K27" s="11" t="s">
-        <x:v>74</x:v>
       </x:c>
     </x:row>
     <x:row r="28" spans="1:11" ht="30" customHeight="1">
       <x:c r="A28" s="12" t="s">
+        <x:v>74</x:v>
+      </x:c>
+      <x:c r="B28" s="12" t="s">
         <x:v>75</x:v>
       </x:c>
-      <x:c r="B28" s="12" t="s">
-        <x:v>76</x:v>
-      </x:c>
       <x:c r="C28" s="12" t="s">
-        <x:v>76</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="D28" s="12" t="s">
-        <x:v>76</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="E28" s="12" t="s">
-        <x:v>76</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="F28" s="12" t="s">
-        <x:v>76</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="G28" s="12" t="s">
-        <x:v>76</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="H28" s="12" t="s">
-        <x:v>76</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="I28" s="12" t="s">
-        <x:v>76</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="J28" s="12" t="s">
-        <x:v>76</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="K28" s="12" t="s">
-        <x:v>76</x:v>
+        <x:v>75</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/data/positions/Posição Consolidada - 7983962.xlsx
+++ b/data/positions/Posição Consolidada - 7983962.xlsx
@@ -19,7 +19,7 @@
     <x:t>XP</x:t>
   </x:si>
   <x:si>
-    <x:t>Conta: 7983962 | 31/08/2026, 17:50</x:t>
+    <x:t>Conta: 7983962 | 01/09/2026, 15:59</x:t>
   </x:si>
   <x:si>
     <x:t>Este é o seu patrimônio</x:t>
@@ -37,7 +37,7 @@
     <x:t>19,7%|Renda Fixa</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 1.033.938,05</x:t>
+    <x:t>R$ 1.034.389,39</x:t>
   </x:si>
   <x:si>
     <x:t>19,60%|Pós-Fixada</x:t>
@@ -97,7 +97,7 @@
     <x:t>46,0%|Operações Compromissadas</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 2.415.584,51</x:t>
+    <x:t>R$ 2.416.645,23</x:t>
   </x:si>
   <x:si>
     <x:t>45,90%|Pós-Fixada</x:t>
@@ -118,10 +118,10 @@
     <x:t>R$ 1.603.779,99</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 1.610.836,28</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 1.609.248,62</x:t>
+    <x:t>R$ 1.611.543,61</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 1.609.796,80</x:t>
   </x:si>
   <x:si>
     <x:t>510.333,00</x:t>
@@ -130,16 +130,16 @@
     <x:t>R$ 801.223,03</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 804.748,24</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 803.955,07</x:t>
+    <x:t>R$ 805.101,61</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 804.228,93</x:t>
   </x:si>
   <x:si>
     <x:t>34,3%|Fundos de Investimento</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 1.804.323,89</x:t>
+    <x:t>R$ 1.805.212,07</x:t>
   </x:si>
   <x:si>
     <x:t>34,30%|Fundos de Renda Fixa Pós-Fixado</x:t>
@@ -160,10 +160,10 @@
     <x:t>Bradesco SKY FIC FIRF Referenciada DI RL</x:t>
   </x:si>
   <x:si>
-    <x:t>31/08/2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 1.444,03</x:t>
+    <x:t>01/09/2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 1.444,78</x:t>
   </x:si>
   <x:si>
     <x:t>15,17</x:t>
@@ -172,10 +172,10 @@
     <x:t>R$ 0,00</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 21.905,59</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 21.783,29</x:t>
+    <x:t>R$ 21.916,91</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 21.792,06</x:t>
   </x:si>
   <x:si>
     <x:t>Bradesco Bancos II FIF CIC RF CP RL</x:t>
@@ -187,25 +187,25 @@
     <x:t>353.356,60</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 521.282,47</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 516.689,62</x:t>
+    <x:t>R$ 521.558,23</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 516.903,33</x:t>
   </x:si>
   <x:si>
     <x:t>Safra Extra Bancos Special FIC FIRF CP</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 141,72</x:t>
+    <x:t>R$ 141,79</x:t>
   </x:si>
   <x:si>
     <x:t>8.898,52</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 1.261.135,83</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 1.253.724,79</x:t>
+    <x:t>R$ 1.261.736,93</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 1.254.190,64</x:t>
   </x:si>
   <x:si>
     <x:t>R$ 2,20</x:t>
@@ -846,10 +846,10 @@
     </x:row>
     <x:row r="4" spans="1:11" ht="30" customHeight="1">
       <x:c r="A4" s="6">
-        <x:v>5253848.65007597</x:v>
+        <x:v>5256248.88452099</x:v>
       </x:c>
       <x:c r="B4" s="7">
-        <x:v>5253846.45007597</x:v>
+        <x:v>5256246.68452099</x:v>
       </x:c>
       <x:c r="C4" s="7">
         <x:v>2.2</x:v>

--- a/data/positions/Posição Consolidada - 7983962.xlsx
+++ b/data/positions/Posição Consolidada - 7983962.xlsx
@@ -19,7 +19,7 @@
     <x:t>XP</x:t>
   </x:si>
   <x:si>
-    <x:t>Conta: 7983962 | 01/09/2026, 15:59</x:t>
+    <x:t>Conta: 7983962 | 04/09/2026, 14:15</x:t>
   </x:si>
   <x:si>
     <x:t>Este é o seu patrimônio</x:t>
@@ -34,13 +34,13 @@
     <x:t>Saldo projetado</x:t>
   </x:si>
   <x:si>
-    <x:t>19,7%|Renda Fixa</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 1.034.389,39</x:t>
-  </x:si>
-  <x:si>
-    <x:t>19,60%|Pós-Fixada</x:t>
+    <x:t>17,4%|Renda Fixa</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 1.035.744,60</x:t>
+  </x:si>
+  <x:si>
+    <x:t>17,30%|Pós-Fixada</x:t>
   </x:si>
   <x:si>
     <x:t>Aplicação</x:t>
@@ -94,13 +94,13 @@
     <x:t>R$ 1.000.949,68</x:t>
   </x:si>
   <x:si>
-    <x:t>46,0%|Operações Compromissadas</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 2.416.645,23</x:t>
-  </x:si>
-  <x:si>
-    <x:t>45,90%|Pós-Fixada</x:t>
+    <x:t>40,6%|Operações Compromissadas</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 2.419.830,15</x:t>
+  </x:si>
+  <x:si>
+    <x:t>40,50%|Pós-Fixada</x:t>
   </x:si>
   <x:si>
     <x:t>17/08/2026</x:t>
@@ -118,10 +118,10 @@
     <x:t>R$ 1.603.779,99</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 1.611.543,61</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 1.609.796,80</x:t>
+    <x:t>R$ 1.613.667,49</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 1.611.442,80</x:t>
   </x:si>
   <x:si>
     <x:t>510.333,00</x:t>
@@ -130,19 +130,19 @@
     <x:t>R$ 801.223,03</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 805.101,61</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 804.228,93</x:t>
-  </x:si>
-  <x:si>
-    <x:t>34,3%|Fundos de Investimento</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 1.805.212,07</x:t>
-  </x:si>
-  <x:si>
-    <x:t>34,30%|Fundos de Renda Fixa Pós-Fixado</x:t>
+    <x:t>R$ 806.162,66</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 805.051,24</x:t>
+  </x:si>
+  <x:si>
+    <x:t>42,1%|Fundos de Investimento</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 2.508.311,08</x:t>
+  </x:si>
+  <x:si>
+    <x:t>42,00%|Fundos de Renda Fixa Pós-Fixado</x:t>
   </x:si>
   <x:si>
     <x:t>Data cota</x:t>
@@ -160,22 +160,22 @@
     <x:t>Bradesco SKY FIC FIRF Referenciada DI RL</x:t>
   </x:si>
   <x:si>
-    <x:t>01/09/2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 1.444,78</x:t>
-  </x:si>
-  <x:si>
-    <x:t>15,17</x:t>
+    <x:t>04/09/2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 1.447,05</x:t>
+  </x:si>
+  <x:si>
+    <x:t>499,16</x:t>
   </x:si>
   <x:si>
     <x:t>R$ 0,00</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 21.916,91</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 21.792,06</x:t>
+    <x:t>R$ 722.305,01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 721.829,80</x:t>
   </x:si>
   <x:si>
     <x:t>Bradesco Bancos II FIF CIC RF CP RL</x:t>
@@ -187,25 +187,25 @@
     <x:t>353.356,60</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 521.558,23</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 516.903,33</x:t>
+    <x:t>R$ 522.397,77</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 517.553,98</x:t>
   </x:si>
   <x:si>
     <x:t>Safra Extra Bancos Special FIC FIRF CP</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 141,79</x:t>
+    <x:t>R$ 142,00</x:t>
   </x:si>
   <x:si>
     <x:t>8.898,52</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 1.261.736,93</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 1.254.190,64</x:t>
+    <x:t>R$ 1.263.608,30</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 1.255.640,95</x:t>
   </x:si>
   <x:si>
     <x:t>R$ 2,20</x:t>
@@ -846,10 +846,10 @@
     </x:row>
     <x:row r="4" spans="1:11" ht="30" customHeight="1">
       <x:c r="A4" s="6">
-        <x:v>5256248.88452099</x:v>
+        <x:v>5963888.02160028</x:v>
       </x:c>
       <x:c r="B4" s="7">
-        <x:v>5256246.68452099</x:v>
+        <x:v>5963885.82160028</x:v>
       </x:c>
       <x:c r="C4" s="7">
         <x:v>2.2</x:v>

--- a/data/positions/Posição Consolidada - 7983962.xlsx
+++ b/data/positions/Posição Consolidada - 7983962.xlsx
@@ -19,7 +19,7 @@
     <x:t>XP</x:t>
   </x:si>
   <x:si>
-    <x:t>Conta: 7983962 | 04/09/2026, 14:15</x:t>
+    <x:t>Conta: 7983962 | 10/09/2026, 14:04</x:t>
   </x:si>
   <x:si>
     <x:t>Este é o seu patrimônio</x:t>
@@ -34,13 +34,13 @@
     <x:t>Saldo projetado</x:t>
   </x:si>
   <x:si>
-    <x:t>17,4%|Renda Fixa</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 1.035.744,60</x:t>
-  </x:si>
-  <x:si>
-    <x:t>17,30%|Pós-Fixada</x:t>
+    <x:t>14,9%|Renda Fixa</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 1.037.101,58</x:t>
+  </x:si>
+  <x:si>
+    <x:t>14,80%|Pós-Fixada</x:t>
   </x:si>
   <x:si>
     <x:t>Aplicação</x:t>
@@ -94,13 +94,13 @@
     <x:t>R$ 1.000.949,68</x:t>
   </x:si>
   <x:si>
-    <x:t>40,6%|Operações Compromissadas</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 2.419.830,15</x:t>
-  </x:si>
-  <x:si>
-    <x:t>40,50%|Pós-Fixada</x:t>
+    <x:t>49,1%|Operações Compromissadas</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 3.423.897,66</x:t>
+  </x:si>
+  <x:si>
+    <x:t>49,10%|Pós-Fixada</x:t>
   </x:si>
   <x:si>
     <x:t>17/08/2026</x:t>
@@ -118,10 +118,10 @@
     <x:t>R$ 1.603.779,99</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 1.613.667,49</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 1.611.442,80</x:t>
+    <x:t>R$ 1.615.794,15</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 1.613.090,97</x:t>
   </x:si>
   <x:si>
     <x:t>510.333,00</x:t>
@@ -130,19 +130,37 @@
     <x:t>R$ 801.223,03</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 806.162,66</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 805.051,24</x:t>
-  </x:si>
-  <x:si>
-    <x:t>42,1%|Fundos de Investimento</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 2.508.311,08</x:t>
-  </x:si>
-  <x:si>
-    <x:t>42,00%|Fundos de Renda Fixa Pós-Fixado</x:t>
+    <x:t>R$ 807.225,11</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 805.874,64</x:t>
+  </x:si>
+  <x:si>
+    <x:t>08/09/2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>09/10/2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>628.930,00</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 1.000.000,00</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 1.000.878,41</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 1.000.680,77</x:t>
+  </x:si>
+  <x:si>
+    <x:t>36,0%|Fundos de Investimento</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 2.512.062,13</x:t>
+  </x:si>
+  <x:si>
+    <x:t>36,00%|Fundos de Renda Fixa Pós-Fixado</x:t>
   </x:si>
   <x:si>
     <x:t>Data cota</x:t>
@@ -160,10 +178,10 @@
     <x:t>Bradesco SKY FIC FIRF Referenciada DI RL</x:t>
   </x:si>
   <x:si>
-    <x:t>04/09/2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 1.447,05</x:t>
+    <x:t>10/09/2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 1.449,20</x:t>
   </x:si>
   <x:si>
     <x:t>499,16</x:t>
@@ -172,10 +190,10 @@
     <x:t>R$ 0,00</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 722.305,01</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 721.829,80</x:t>
+    <x:t>R$ 723.377,70</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 722.103,33</x:t>
   </x:si>
   <x:si>
     <x:t>Bradesco Bancos II FIF CIC RF CP RL</x:t>
@@ -187,25 +205,25 @@
     <x:t>353.356,60</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 522.397,77</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 517.553,98</x:t>
+    <x:t>R$ 523.213,95</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 518.186,52</x:t>
   </x:si>
   <x:si>
     <x:t>Safra Extra Bancos Special FIC FIRF CP</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 142,00</x:t>
+    <x:t>R$ 142,21</x:t>
   </x:si>
   <x:si>
     <x:t>8.898,52</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 1.263.608,30</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 1.255.640,95</x:t>
+    <x:t>R$ 1.265.470,48</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 1.257.084,14</x:t>
   </x:si>
   <x:si>
     <x:t>R$ 2,20</x:t>
@@ -786,7 +804,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:K28"/>
+  <x:dimension ref="A1:K29"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="38.282054" style="0" customWidth="1"/>
@@ -846,10 +864,10 @@
     </x:row>
     <x:row r="4" spans="1:11" ht="30" customHeight="1">
       <x:c r="A4" s="6">
-        <x:v>5963888.02160028</x:v>
+        <x:v>6973063.57344769</x:v>
       </x:c>
       <x:c r="B4" s="7">
-        <x:v>5963885.82160028</x:v>
+        <x:v>6973061.37344769</x:v>
       </x:c>
       <x:c r="C4" s="7">
         <x:v>2.2</x:v>
@@ -1093,125 +1111,127 @@
       <x:c r="K15" s="3"/>
     </x:row>
     <x:row r="16" spans="1:11" ht="30" customHeight="1">
-      <x:c r="A16" s="12"/>
-      <x:c r="B16" s="12" t="s">
+      <x:c r="A16" s="13"/>
+      <x:c r="B16" s="13" t="s">
         <x:v>29</x:v>
       </x:c>
-      <x:c r="C16" s="12"/>
-      <x:c r="D16" s="12" t="s">
+      <x:c r="C16" s="13"/>
+      <x:c r="D16" s="13" t="s">
         <x:v>30</x:v>
       </x:c>
-      <x:c r="E16" s="12" t="s">
+      <x:c r="E16" s="13" t="s">
         <x:v>31</x:v>
       </x:c>
-      <x:c r="F16" s="12" t="s">
+      <x:c r="F16" s="13" t="s">
         <x:v>36</x:v>
       </x:c>
-      <x:c r="G16" s="12" t="s">
+      <x:c r="G16" s="13" t="s">
         <x:v>24</x:v>
       </x:c>
-      <x:c r="H16" s="12" t="s">
+      <x:c r="H16" s="13" t="s">
         <x:v>37</x:v>
       </x:c>
-      <x:c r="I16" s="12" t="s">
+      <x:c r="I16" s="13" t="s">
         <x:v>38</x:v>
       </x:c>
-      <x:c r="J16" s="12" t="s">
+      <x:c r="J16" s="13" t="s">
         <x:v>39</x:v>
       </x:c>
       <x:c r="K16" s="3"/>
     </x:row>
-    <x:row r="17" spans="1:11">
-      <x:c r="A17" s="4"/>
-      <x:c r="B17" s="4"/>
-      <x:c r="C17" s="4"/>
-      <x:c r="D17" s="4"/>
-      <x:c r="E17" s="4"/>
-      <x:c r="F17" s="4"/>
-      <x:c r="G17" s="4"/>
-      <x:c r="H17" s="4"/>
-      <x:c r="I17" s="4"/>
-      <x:c r="J17" s="4"/>
-      <x:c r="K17" s="4"/>
-    </x:row>
-    <x:row r="18" spans="1:11" ht="45" customHeight="1">
-      <x:c r="A18" s="8" t="s">
+    <x:row r="17" spans="1:11" ht="30" customHeight="1">
+      <x:c r="A17" s="12"/>
+      <x:c r="B17" s="12" t="s">
         <x:v>40</x:v>
       </x:c>
-      <x:c r="B18" s="9"/>
-      <x:c r="C18" s="9"/>
-      <x:c r="D18" s="9"/>
-      <x:c r="E18" s="9"/>
-      <x:c r="F18" s="9"/>
-      <x:c r="G18" s="10" t="s">
+      <x:c r="C17" s="12"/>
+      <x:c r="D17" s="12" t="s">
         <x:v>41</x:v>
       </x:c>
-      <x:c r="H18" s="3"/>
-      <x:c r="I18" s="3"/>
-      <x:c r="J18" s="3"/>
-      <x:c r="K18" s="3"/>
-    </x:row>
-    <x:row r="19" spans="1:11">
-      <x:c r="A19" s="4"/>
-      <x:c r="B19" s="4"/>
-      <x:c r="C19" s="4"/>
-      <x:c r="D19" s="4"/>
-      <x:c r="E19" s="4"/>
-      <x:c r="F19" s="4"/>
-      <x:c r="G19" s="4"/>
+      <x:c r="E17" s="12" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="F17" s="12" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="G17" s="12" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="H17" s="12" t="s">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="I17" s="12" t="s">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="J17" s="12" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="K17" s="3"/>
+    </x:row>
+    <x:row r="18" spans="1:11">
+      <x:c r="A18" s="4"/>
+      <x:c r="B18" s="4"/>
+      <x:c r="C18" s="4"/>
+      <x:c r="D18" s="4"/>
+      <x:c r="E18" s="4"/>
+      <x:c r="F18" s="4"/>
+      <x:c r="G18" s="4"/>
+      <x:c r="H18" s="4"/>
+      <x:c r="I18" s="4"/>
+      <x:c r="J18" s="4"/>
+      <x:c r="K18" s="4"/>
+    </x:row>
+    <x:row r="19" spans="1:11" ht="45" customHeight="1">
+      <x:c r="A19" s="8" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="B19" s="9"/>
+      <x:c r="C19" s="9"/>
+      <x:c r="D19" s="9"/>
+      <x:c r="E19" s="9"/>
+      <x:c r="F19" s="9"/>
+      <x:c r="G19" s="10" t="s">
+        <x:v>47</x:v>
+      </x:c>
       <x:c r="H19" s="3"/>
       <x:c r="I19" s="3"/>
       <x:c r="J19" s="3"/>
       <x:c r="K19" s="3"/>
     </x:row>
-    <x:row r="20" spans="1:11" ht="35.1" customHeight="1">
-      <x:c r="A20" s="11" t="s">
-        <x:v>42</x:v>
-      </x:c>
-      <x:c r="B20" s="11" t="s">
-        <x:v>43</x:v>
-      </x:c>
-      <x:c r="C20" s="11" t="s">
-        <x:v>44</x:v>
-      </x:c>
-      <x:c r="D20" s="11" t="s">
-        <x:v>45</x:v>
-      </x:c>
-      <x:c r="E20" s="11" t="s">
-        <x:v>46</x:v>
-      </x:c>
-      <x:c r="F20" s="11" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="G20" s="11" t="s">
-        <x:v>17</x:v>
-      </x:c>
+    <x:row r="20" spans="1:11">
+      <x:c r="A20" s="4"/>
+      <x:c r="B20" s="4"/>
+      <x:c r="C20" s="4"/>
+      <x:c r="D20" s="4"/>
+      <x:c r="E20" s="4"/>
+      <x:c r="F20" s="4"/>
+      <x:c r="G20" s="4"/>
       <x:c r="H20" s="3"/>
       <x:c r="I20" s="3"/>
       <x:c r="J20" s="3"/>
       <x:c r="K20" s="3"/>
     </x:row>
-    <x:row r="21" spans="1:11" ht="30" customHeight="1">
-      <x:c r="A21" s="13" t="s">
-        <x:v>47</x:v>
-      </x:c>
-      <x:c r="B21" s="13" t="s">
+    <x:row r="21" spans="1:11" ht="35.1" customHeight="1">
+      <x:c r="A21" s="11" t="s">
         <x:v>48</x:v>
       </x:c>
-      <x:c r="C21" s="13" t="s">
+      <x:c r="B21" s="11" t="s">
         <x:v>49</x:v>
       </x:c>
-      <x:c r="D21" s="13" t="s">
+      <x:c r="C21" s="11" t="s">
         <x:v>50</x:v>
       </x:c>
-      <x:c r="E21" s="13" t="s">
+      <x:c r="D21" s="11" t="s">
         <x:v>51</x:v>
       </x:c>
-      <x:c r="F21" s="13" t="s">
+      <x:c r="E21" s="11" t="s">
         <x:v>52</x:v>
       </x:c>
-      <x:c r="G21" s="13" t="s">
-        <x:v>53</x:v>
+      <x:c r="F21" s="11" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="G21" s="11" t="s">
+        <x:v>17</x:v>
       </x:c>
       <x:c r="H21" s="3"/>
       <x:c r="I21" s="3"/>
@@ -1220,10 +1240,10 @@
     </x:row>
     <x:row r="22" spans="1:11" ht="30" customHeight="1">
       <x:c r="A22" s="13" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="B22" s="13" t="s">
         <x:v>54</x:v>
-      </x:c>
-      <x:c r="B22" s="13" t="s">
-        <x:v>48</x:v>
       </x:c>
       <x:c r="C22" s="13" t="s">
         <x:v>55</x:v>
@@ -1232,13 +1252,13 @@
         <x:v>56</x:v>
       </x:c>
       <x:c r="E22" s="13" t="s">
-        <x:v>51</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="F22" s="13" t="s">
-        <x:v>57</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="G22" s="13" t="s">
-        <x:v>58</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="H22" s="3"/>
       <x:c r="I22" s="3"/>
@@ -1246,143 +1266,170 @@
       <x:c r="K22" s="3"/>
     </x:row>
     <x:row r="23" spans="1:11" ht="30" customHeight="1">
-      <x:c r="A23" s="12" t="s">
-        <x:v>59</x:v>
-      </x:c>
-      <x:c r="B23" s="12" t="s">
-        <x:v>48</x:v>
-      </x:c>
-      <x:c r="C23" s="12" t="s">
+      <x:c r="A23" s="13" t="s">
         <x:v>60</x:v>
       </x:c>
-      <x:c r="D23" s="12" t="s">
+      <x:c r="B23" s="13" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="C23" s="13" t="s">
         <x:v>61</x:v>
       </x:c>
-      <x:c r="E23" s="12" t="s">
-        <x:v>51</x:v>
-      </x:c>
-      <x:c r="F23" s="12" t="s">
+      <x:c r="D23" s="13" t="s">
         <x:v>62</x:v>
       </x:c>
-      <x:c r="G23" s="12" t="s">
+      <x:c r="E23" s="13" t="s">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="F23" s="13" t="s">
         <x:v>63</x:v>
+      </x:c>
+      <x:c r="G23" s="13" t="s">
+        <x:v>64</x:v>
       </x:c>
       <x:c r="H23" s="3"/>
       <x:c r="I23" s="3"/>
       <x:c r="J23" s="3"/>
       <x:c r="K23" s="3"/>
     </x:row>
-    <x:row r="24" spans="1:11">
-      <x:c r="A24" s="4"/>
-      <x:c r="B24" s="4"/>
-      <x:c r="C24" s="4"/>
-      <x:c r="D24" s="4"/>
-      <x:c r="E24" s="4"/>
-      <x:c r="F24" s="4"/>
-      <x:c r="G24" s="4"/>
-      <x:c r="H24" s="4"/>
-      <x:c r="I24" s="4"/>
-      <x:c r="J24" s="4"/>
-      <x:c r="K24" s="4"/>
-    </x:row>
-    <x:row r="25" spans="1:11" ht="45" customHeight="1">
-      <x:c r="A25" s="8" t="s">
+    <x:row r="24" spans="1:11" ht="30" customHeight="1">
+      <x:c r="A24" s="12" t="s">
+        <x:v>65</x:v>
+      </x:c>
+      <x:c r="B24" s="12" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="C24" s="12" t="s">
+        <x:v>66</x:v>
+      </x:c>
+      <x:c r="D24" s="12" t="s">
+        <x:v>67</x:v>
+      </x:c>
+      <x:c r="E24" s="12" t="s">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="F24" s="12" t="s">
+        <x:v>68</x:v>
+      </x:c>
+      <x:c r="G24" s="12" t="s">
+        <x:v>69</x:v>
+      </x:c>
+      <x:c r="H24" s="3"/>
+      <x:c r="I24" s="3"/>
+      <x:c r="J24" s="3"/>
+      <x:c r="K24" s="3"/>
+    </x:row>
+    <x:row r="25" spans="1:11">
+      <x:c r="A25" s="4"/>
+      <x:c r="B25" s="4"/>
+      <x:c r="C25" s="4"/>
+      <x:c r="D25" s="4"/>
+      <x:c r="E25" s="4"/>
+      <x:c r="F25" s="4"/>
+      <x:c r="G25" s="4"/>
+      <x:c r="H25" s="4"/>
+      <x:c r="I25" s="4"/>
+      <x:c r="J25" s="4"/>
+      <x:c r="K25" s="4"/>
+    </x:row>
+    <x:row r="26" spans="1:11" ht="45" customHeight="1">
+      <x:c r="A26" s="8" t="s">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="B25" s="9"/>
-      <x:c r="C25" s="9"/>
-      <x:c r="D25" s="9"/>
-      <x:c r="E25" s="9"/>
-      <x:c r="F25" s="9"/>
-      <x:c r="G25" s="9"/>
-      <x:c r="H25" s="9"/>
-      <x:c r="I25" s="9"/>
-      <x:c r="J25" s="9"/>
-      <x:c r="K25" s="10" t="s">
-        <x:v>64</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="26" spans="1:11">
-      <x:c r="A26" s="4"/>
-      <x:c r="B26" s="4"/>
-      <x:c r="C26" s="4"/>
-      <x:c r="D26" s="4"/>
-      <x:c r="E26" s="4"/>
-      <x:c r="F26" s="4"/>
-      <x:c r="G26" s="4"/>
-      <x:c r="H26" s="4"/>
-      <x:c r="I26" s="4"/>
-      <x:c r="J26" s="4"/>
-      <x:c r="K26" s="4"/>
-    </x:row>
-    <x:row r="27" spans="1:11" ht="35.1" customHeight="1">
-      <x:c r="A27" s="11" t="s">
+      <x:c r="B26" s="9"/>
+      <x:c r="C26" s="9"/>
+      <x:c r="D26" s="9"/>
+      <x:c r="E26" s="9"/>
+      <x:c r="F26" s="9"/>
+      <x:c r="G26" s="9"/>
+      <x:c r="H26" s="9"/>
+      <x:c r="I26" s="9"/>
+      <x:c r="J26" s="9"/>
+      <x:c r="K26" s="10" t="s">
+        <x:v>70</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="27" spans="1:11">
+      <x:c r="A27" s="4"/>
+      <x:c r="B27" s="4"/>
+      <x:c r="C27" s="4"/>
+      <x:c r="D27" s="4"/>
+      <x:c r="E27" s="4"/>
+      <x:c r="F27" s="4"/>
+      <x:c r="G27" s="4"/>
+      <x:c r="H27" s="4"/>
+      <x:c r="I27" s="4"/>
+      <x:c r="J27" s="4"/>
+      <x:c r="K27" s="4"/>
+    </x:row>
+    <x:row r="28" spans="1:11" ht="35.1" customHeight="1">
+      <x:c r="A28" s="11" t="s">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="B27" s="11" t="s">
+      <x:c r="B28" s="11" t="s">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="C27" s="11" t="s">
-        <x:v>65</x:v>
-      </x:c>
-      <x:c r="D27" s="11" t="s">
-        <x:v>66</x:v>
-      </x:c>
-      <x:c r="E27" s="11" t="s">
-        <x:v>67</x:v>
-      </x:c>
-      <x:c r="F27" s="11" t="s">
-        <x:v>68</x:v>
-      </x:c>
-      <x:c r="G27" s="11" t="s">
-        <x:v>69</x:v>
-      </x:c>
-      <x:c r="H27" s="11" t="s">
-        <x:v>70</x:v>
-      </x:c>
-      <x:c r="I27" s="11" t="s">
+      <x:c r="C28" s="11" t="s">
         <x:v>71</x:v>
       </x:c>
-      <x:c r="J27" s="11" t="s">
+      <x:c r="D28" s="11" t="s">
         <x:v>72</x:v>
       </x:c>
-      <x:c r="K27" s="11" t="s">
+      <x:c r="E28" s="11" t="s">
         <x:v>73</x:v>
       </x:c>
-    </x:row>
-    <x:row r="28" spans="1:11" ht="30" customHeight="1">
-      <x:c r="A28" s="12" t="s">
+      <x:c r="F28" s="11" t="s">
         <x:v>74</x:v>
       </x:c>
-      <x:c r="B28" s="12" t="s">
+      <x:c r="G28" s="11" t="s">
         <x:v>75</x:v>
       </x:c>
-      <x:c r="C28" s="12" t="s">
-        <x:v>75</x:v>
-      </x:c>
-      <x:c r="D28" s="12" t="s">
-        <x:v>75</x:v>
-      </x:c>
-      <x:c r="E28" s="12" t="s">
-        <x:v>75</x:v>
-      </x:c>
-      <x:c r="F28" s="12" t="s">
-        <x:v>75</x:v>
-      </x:c>
-      <x:c r="G28" s="12" t="s">
-        <x:v>75</x:v>
-      </x:c>
-      <x:c r="H28" s="12" t="s">
-        <x:v>75</x:v>
-      </x:c>
-      <x:c r="I28" s="12" t="s">
-        <x:v>75</x:v>
-      </x:c>
-      <x:c r="J28" s="12" t="s">
-        <x:v>75</x:v>
-      </x:c>
-      <x:c r="K28" s="12" t="s">
-        <x:v>75</x:v>
+      <x:c r="H28" s="11" t="s">
+        <x:v>76</x:v>
+      </x:c>
+      <x:c r="I28" s="11" t="s">
+        <x:v>77</x:v>
+      </x:c>
+      <x:c r="J28" s="11" t="s">
+        <x:v>78</x:v>
+      </x:c>
+      <x:c r="K28" s="11" t="s">
+        <x:v>79</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="29" spans="1:11" ht="30" customHeight="1">
+      <x:c r="A29" s="12" t="s">
+        <x:v>80</x:v>
+      </x:c>
+      <x:c r="B29" s="12" t="s">
+        <x:v>81</x:v>
+      </x:c>
+      <x:c r="C29" s="12" t="s">
+        <x:v>81</x:v>
+      </x:c>
+      <x:c r="D29" s="12" t="s">
+        <x:v>81</x:v>
+      </x:c>
+      <x:c r="E29" s="12" t="s">
+        <x:v>81</x:v>
+      </x:c>
+      <x:c r="F29" s="12" t="s">
+        <x:v>81</x:v>
+      </x:c>
+      <x:c r="G29" s="12" t="s">
+        <x:v>81</x:v>
+      </x:c>
+      <x:c r="H29" s="12" t="s">
+        <x:v>81</x:v>
+      </x:c>
+      <x:c r="I29" s="12" t="s">
+        <x:v>81</x:v>
+      </x:c>
+      <x:c r="J29" s="12" t="s">
+        <x:v>81</x:v>
+      </x:c>
+      <x:c r="K29" s="12" t="s">
+        <x:v>81</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -1391,8 +1438,8 @@
     <x:mergeCell ref="F1:G1"/>
     <x:mergeCell ref="A7:F7"/>
     <x:mergeCell ref="A12:F12"/>
-    <x:mergeCell ref="A18:F18"/>
-    <x:mergeCell ref="A25:J25"/>
+    <x:mergeCell ref="A19:F19"/>
+    <x:mergeCell ref="A26:J26"/>
   </x:mergeCells>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>

--- a/data/positions/Posição Consolidada - 7983962.xlsx
+++ b/data/positions/Posição Consolidada - 7983962.xlsx
@@ -19,7 +19,7 @@
     <x:t>XP</x:t>
   </x:si>
   <x:si>
-    <x:t>Conta: 7983962 | 10/09/2026, 14:04</x:t>
+    <x:t>Conta: 7983962 | 16/09/2026, 08:43</x:t>
   </x:si>
   <x:si>
     <x:t>Este é o seu patrimônio</x:t>
@@ -34,13 +34,13 @@
     <x:t>Saldo projetado</x:t>
   </x:si>
   <x:si>
-    <x:t>14,9%|Renda Fixa</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 1.037.101,58</x:t>
-  </x:si>
-  <x:si>
-    <x:t>14,80%|Pós-Fixada</x:t>
+    <x:t>11,0%|Renda Fixa</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 1.038.913,66</x:t>
+  </x:si>
+  <x:si>
+    <x:t>10,90%|Pós-Fixada</x:t>
   </x:si>
   <x:si>
     <x:t>Aplicação</x:t>
@@ -94,13 +94,13 @@
     <x:t>R$ 1.000.949,68</x:t>
   </x:si>
   <x:si>
-    <x:t>49,1%|Operações Compromissadas</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 3.423.897,66</x:t>
-  </x:si>
-  <x:si>
-    <x:t>49,10%|Pós-Fixada</x:t>
+    <x:t>36,1%|Operações Compromissadas</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 3.428.611,10</x:t>
+  </x:si>
+  <x:si>
+    <x:t>36,10%|Pós-Fixada</x:t>
   </x:si>
   <x:si>
     <x:t>17/08/2026</x:t>
@@ -112,28 +112,28 @@
     <x:t>85,00% CDI</x:t>
   </x:si>
   <x:si>
-    <x:t>1.015.050,00</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 1.603.779,99</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 1.615.794,15</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 1.613.090,97</x:t>
-  </x:si>
-  <x:si>
-    <x:t>510.333,00</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 801.223,03</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 807.225,11</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 805.874,64</x:t>
+    <x:t>1.014.233,00</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 1.602.489,13</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 1.617.331,25</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 1.613.991,77</x:t>
+  </x:si>
+  <x:si>
+    <x:t>510.332,00</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 801.221,46</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 808.642,30</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 806.972,61</x:t>
   </x:si>
   <x:si>
     <x:t>08/09/2026</x:t>
@@ -148,19 +148,19 @@
     <x:t>R$ 1.000.000,00</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 1.000.878,41</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 1.000.680,77</x:t>
-  </x:si>
-  <x:si>
-    <x:t>36,0%|Fundos de Investimento</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 2.512.062,13</x:t>
-  </x:si>
-  <x:si>
-    <x:t>36,00%|Fundos de Renda Fixa Pós-Fixado</x:t>
+    <x:t>R$ 1.002.637,55</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 1.002.044,10</x:t>
+  </x:si>
+  <x:si>
+    <x:t>52,9%|Fundos de Investimento</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 5.017.170,75</x:t>
+  </x:si>
+  <x:si>
+    <x:t>52,80%|Fundos de Renda Fixa Pós-Fixado</x:t>
   </x:si>
   <x:si>
     <x:t>Data cota</x:t>
@@ -175,25 +175,40 @@
     <x:t>Em cotização</x:t>
   </x:si>
   <x:si>
+    <x:t>XP Bancos FIRF Referenciada DI CP RL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>15/09/2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 1,94</x:t>
+  </x:si>
+  <x:si>
+    <x:t>772.979,35</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 0,00</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 1.500.781,15</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 1.500.024,21</x:t>
+  </x:si>
+  <x:si>
     <x:t>Bradesco SKY FIC FIRF Referenciada DI RL</x:t>
   </x:si>
   <x:si>
-    <x:t>10/09/2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 1.449,20</x:t>
-  </x:si>
-  <x:si>
-    <x:t>499,16</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 0,00</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 723.377,70</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 722.103,33</x:t>
+    <x:t>R$ 1.451,45</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1.188,48</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 1.725.011,61</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 1.722.655,31</x:t>
   </x:si>
   <x:si>
     <x:t>Bradesco Bancos II FIF CIC RF CP RL</x:t>
@@ -205,28 +220,28 @@
     <x:t>353.356,60</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 523.213,95</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 518.186,52</x:t>
+    <x:t>R$ 524.029,25</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 518.818,37</x:t>
   </x:si>
   <x:si>
     <x:t>Safra Extra Bancos Special FIC FIRF CP</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 142,21</x:t>
+    <x:t>R$ 142,42</x:t>
   </x:si>
   <x:si>
     <x:t>8.898,52</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 1.265.470,48</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 1.257.084,14</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 2,20</x:t>
+    <x:t>R$ 1.267.348,74</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 1.258.539,80</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 222,42</x:t>
   </x:si>
   <x:si>
     <x:t>Resgate de fundo pendente</x:t>
@@ -256,7 +271,7 @@
     <x:t>Saldo Projetado  (D &gt; 3)</x:t>
   </x:si>
   <x:si>
-    <x:t>2,2</x:t>
+    <x:t>222,42</x:t>
   </x:si>
   <x:si>
     <x:t>0</x:t>
@@ -804,7 +819,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:K29"/>
+  <x:dimension ref="A1:K30"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="38.282054" style="0" customWidth="1"/>
@@ -864,13 +879,13 @@
     </x:row>
     <x:row r="4" spans="1:11" ht="30" customHeight="1">
       <x:c r="A4" s="6">
-        <x:v>6973063.57344769</x:v>
+        <x:v>9484917.92591729</x:v>
       </x:c>
       <x:c r="B4" s="7">
-        <x:v>6973061.37344769</x:v>
+        <x:v>9484695.50591729</x:v>
       </x:c>
       <x:c r="C4" s="7">
-        <x:v>2.2</x:v>
+        <x:v>222.42</x:v>
       </x:c>
       <x:c r="D4" s="7">
         <x:v>0</x:v>
@@ -1293,25 +1308,25 @@
       <x:c r="K23" s="3"/>
     </x:row>
     <x:row r="24" spans="1:11" ht="30" customHeight="1">
-      <x:c r="A24" s="12" t="s">
+      <x:c r="A24" s="13" t="s">
         <x:v>65</x:v>
       </x:c>
-      <x:c r="B24" s="12" t="s">
+      <x:c r="B24" s="13" t="s">
         <x:v>54</x:v>
       </x:c>
-      <x:c r="C24" s="12" t="s">
+      <x:c r="C24" s="13" t="s">
         <x:v>66</x:v>
       </x:c>
-      <x:c r="D24" s="12" t="s">
+      <x:c r="D24" s="13" t="s">
         <x:v>67</x:v>
       </x:c>
-      <x:c r="E24" s="12" t="s">
+      <x:c r="E24" s="13" t="s">
         <x:v>57</x:v>
       </x:c>
-      <x:c r="F24" s="12" t="s">
+      <x:c r="F24" s="13" t="s">
         <x:v>68</x:v>
       </x:c>
-      <x:c r="G24" s="12" t="s">
+      <x:c r="G24" s="13" t="s">
         <x:v>69</x:v>
       </x:c>
       <x:c r="H24" s="3"/>
@@ -1319,117 +1334,144 @@
       <x:c r="J24" s="3"/>
       <x:c r="K24" s="3"/>
     </x:row>
-    <x:row r="25" spans="1:11">
-      <x:c r="A25" s="4"/>
-      <x:c r="B25" s="4"/>
-      <x:c r="C25" s="4"/>
-      <x:c r="D25" s="4"/>
-      <x:c r="E25" s="4"/>
-      <x:c r="F25" s="4"/>
-      <x:c r="G25" s="4"/>
-      <x:c r="H25" s="4"/>
-      <x:c r="I25" s="4"/>
-      <x:c r="J25" s="4"/>
-      <x:c r="K25" s="4"/>
-    </x:row>
-    <x:row r="26" spans="1:11" ht="45" customHeight="1">
-      <x:c r="A26" s="8" t="s">
+    <x:row r="25" spans="1:11" ht="30" customHeight="1">
+      <x:c r="A25" s="12" t="s">
+        <x:v>70</x:v>
+      </x:c>
+      <x:c r="B25" s="12" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="C25" s="12" t="s">
+        <x:v>71</x:v>
+      </x:c>
+      <x:c r="D25" s="12" t="s">
+        <x:v>72</x:v>
+      </x:c>
+      <x:c r="E25" s="12" t="s">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="F25" s="12" t="s">
+        <x:v>73</x:v>
+      </x:c>
+      <x:c r="G25" s="12" t="s">
+        <x:v>74</x:v>
+      </x:c>
+      <x:c r="H25" s="3"/>
+      <x:c r="I25" s="3"/>
+      <x:c r="J25" s="3"/>
+      <x:c r="K25" s="3"/>
+    </x:row>
+    <x:row r="26" spans="1:11">
+      <x:c r="A26" s="4"/>
+      <x:c r="B26" s="4"/>
+      <x:c r="C26" s="4"/>
+      <x:c r="D26" s="4"/>
+      <x:c r="E26" s="4"/>
+      <x:c r="F26" s="4"/>
+      <x:c r="G26" s="4"/>
+      <x:c r="H26" s="4"/>
+      <x:c r="I26" s="4"/>
+      <x:c r="J26" s="4"/>
+      <x:c r="K26" s="4"/>
+    </x:row>
+    <x:row r="27" spans="1:11" ht="45" customHeight="1">
+      <x:c r="A27" s="8" t="s">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="B26" s="9"/>
-      <x:c r="C26" s="9"/>
-      <x:c r="D26" s="9"/>
-      <x:c r="E26" s="9"/>
-      <x:c r="F26" s="9"/>
-      <x:c r="G26" s="9"/>
-      <x:c r="H26" s="9"/>
-      <x:c r="I26" s="9"/>
-      <x:c r="J26" s="9"/>
-      <x:c r="K26" s="10" t="s">
-        <x:v>70</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="27" spans="1:11">
-      <x:c r="A27" s="4"/>
-      <x:c r="B27" s="4"/>
-      <x:c r="C27" s="4"/>
-      <x:c r="D27" s="4"/>
-      <x:c r="E27" s="4"/>
-      <x:c r="F27" s="4"/>
-      <x:c r="G27" s="4"/>
-      <x:c r="H27" s="4"/>
-      <x:c r="I27" s="4"/>
-      <x:c r="J27" s="4"/>
-      <x:c r="K27" s="4"/>
-    </x:row>
-    <x:row r="28" spans="1:11" ht="35.1" customHeight="1">
-      <x:c r="A28" s="11" t="s">
+      <x:c r="B27" s="9"/>
+      <x:c r="C27" s="9"/>
+      <x:c r="D27" s="9"/>
+      <x:c r="E27" s="9"/>
+      <x:c r="F27" s="9"/>
+      <x:c r="G27" s="9"/>
+      <x:c r="H27" s="9"/>
+      <x:c r="I27" s="9"/>
+      <x:c r="J27" s="9"/>
+      <x:c r="K27" s="10" t="s">
+        <x:v>75</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="28" spans="1:11">
+      <x:c r="A28" s="4"/>
+      <x:c r="B28" s="4"/>
+      <x:c r="C28" s="4"/>
+      <x:c r="D28" s="4"/>
+      <x:c r="E28" s="4"/>
+      <x:c r="F28" s="4"/>
+      <x:c r="G28" s="4"/>
+      <x:c r="H28" s="4"/>
+      <x:c r="I28" s="4"/>
+      <x:c r="J28" s="4"/>
+      <x:c r="K28" s="4"/>
+    </x:row>
+    <x:row r="29" spans="1:11" ht="35.1" customHeight="1">
+      <x:c r="A29" s="11" t="s">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="B28" s="11" t="s">
+      <x:c r="B29" s="11" t="s">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="C28" s="11" t="s">
-        <x:v>71</x:v>
-      </x:c>
-      <x:c r="D28" s="11" t="s">
-        <x:v>72</x:v>
-      </x:c>
-      <x:c r="E28" s="11" t="s">
-        <x:v>73</x:v>
-      </x:c>
-      <x:c r="F28" s="11" t="s">
-        <x:v>74</x:v>
-      </x:c>
-      <x:c r="G28" s="11" t="s">
-        <x:v>75</x:v>
-      </x:c>
-      <x:c r="H28" s="11" t="s">
+      <x:c r="C29" s="11" t="s">
         <x:v>76</x:v>
       </x:c>
-      <x:c r="I28" s="11" t="s">
+      <x:c r="D29" s="11" t="s">
         <x:v>77</x:v>
       </x:c>
-      <x:c r="J28" s="11" t="s">
+      <x:c r="E29" s="11" t="s">
         <x:v>78</x:v>
       </x:c>
-      <x:c r="K28" s="11" t="s">
+      <x:c r="F29" s="11" t="s">
         <x:v>79</x:v>
       </x:c>
-    </x:row>
-    <x:row r="29" spans="1:11" ht="30" customHeight="1">
-      <x:c r="A29" s="12" t="s">
+      <x:c r="G29" s="11" t="s">
         <x:v>80</x:v>
       </x:c>
-      <x:c r="B29" s="12" t="s">
+      <x:c r="H29" s="11" t="s">
         <x:v>81</x:v>
       </x:c>
-      <x:c r="C29" s="12" t="s">
-        <x:v>81</x:v>
-      </x:c>
-      <x:c r="D29" s="12" t="s">
-        <x:v>81</x:v>
-      </x:c>
-      <x:c r="E29" s="12" t="s">
-        <x:v>81</x:v>
-      </x:c>
-      <x:c r="F29" s="12" t="s">
-        <x:v>81</x:v>
-      </x:c>
-      <x:c r="G29" s="12" t="s">
-        <x:v>81</x:v>
-      </x:c>
-      <x:c r="H29" s="12" t="s">
-        <x:v>81</x:v>
-      </x:c>
-      <x:c r="I29" s="12" t="s">
-        <x:v>81</x:v>
-      </x:c>
-      <x:c r="J29" s="12" t="s">
-        <x:v>81</x:v>
-      </x:c>
-      <x:c r="K29" s="12" t="s">
-        <x:v>81</x:v>
+      <x:c r="I29" s="11" t="s">
+        <x:v>82</x:v>
+      </x:c>
+      <x:c r="J29" s="11" t="s">
+        <x:v>83</x:v>
+      </x:c>
+      <x:c r="K29" s="11" t="s">
+        <x:v>84</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="30" spans="1:11" ht="30" customHeight="1">
+      <x:c r="A30" s="12" t="s">
+        <x:v>85</x:v>
+      </x:c>
+      <x:c r="B30" s="12" t="s">
+        <x:v>86</x:v>
+      </x:c>
+      <x:c r="C30" s="12" t="s">
+        <x:v>86</x:v>
+      </x:c>
+      <x:c r="D30" s="12" t="s">
+        <x:v>86</x:v>
+      </x:c>
+      <x:c r="E30" s="12" t="s">
+        <x:v>86</x:v>
+      </x:c>
+      <x:c r="F30" s="12" t="s">
+        <x:v>86</x:v>
+      </x:c>
+      <x:c r="G30" s="12" t="s">
+        <x:v>86</x:v>
+      </x:c>
+      <x:c r="H30" s="12" t="s">
+        <x:v>86</x:v>
+      </x:c>
+      <x:c r="I30" s="12" t="s">
+        <x:v>86</x:v>
+      </x:c>
+      <x:c r="J30" s="12" t="s">
+        <x:v>86</x:v>
+      </x:c>
+      <x:c r="K30" s="12" t="s">
+        <x:v>86</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -1439,7 +1481,7 @@
     <x:mergeCell ref="A7:F7"/>
     <x:mergeCell ref="A12:F12"/>
     <x:mergeCell ref="A19:F19"/>
-    <x:mergeCell ref="A26:J26"/>
+    <x:mergeCell ref="A27:J27"/>
   </x:mergeCells>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>

--- a/data/positions/Posição Consolidada - 7983962.xlsx
+++ b/data/positions/Posição Consolidada - 7983962.xlsx
@@ -19,7 +19,7 @@
     <x:t>XP</x:t>
   </x:si>
   <x:si>
-    <x:t>Conta: 7983962 | 16/09/2026, 08:43</x:t>
+    <x:t>Conta: 7983962 | 21/09/2026, 16:40</x:t>
   </x:si>
   <x:si>
     <x:t>Este é o seu patrimônio</x:t>
@@ -34,13 +34,13 @@
     <x:t>Saldo projetado</x:t>
   </x:si>
   <x:si>
-    <x:t>11,0%|Renda Fixa</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 1.038.913,66</x:t>
-  </x:si>
-  <x:si>
-    <x:t>10,90%|Pós-Fixada</x:t>
+    <x:t>26,9%|Renda Fixa</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 2.232.803,73</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26,90%|Pós-Fixada</x:t>
   </x:si>
   <x:si>
     <x:t>Aplicação</x:t>
@@ -94,73 +94,70 @@
     <x:t>R$ 1.000.949,68</x:t>
   </x:si>
   <x:si>
-    <x:t>36,1%|Operações Compromissadas</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 3.428.611,10</x:t>
-  </x:si>
-  <x:si>
-    <x:t>36,10%|Pós-Fixada</x:t>
-  </x:si>
-  <x:si>
-    <x:t>17/08/2026</x:t>
+    <x:t>R$ 1.040.259,47</x:t>
+  </x:si>
+  <x:si>
+    <x:t>LCI CEF - MAI/2027</x:t>
+  </x:si>
+  <x:si>
+    <x:t>17/09/2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>14/05/2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>04/05/2027</x:t>
+  </x:si>
+  <x:si>
+    <x:t>85,50% CDI</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1,00</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 1.191.509,24</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 1.192.544,26</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 1.191.654,14</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2,72%|Operações Compromissadas</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 225.862,69</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2,70%|Pós-Fixada</x:t>
   </x:si>
   <x:si>
     <x:t>18/09/2026</x:t>
   </x:si>
   <x:si>
+    <x:t>22/10/2026</x:t>
+  </x:si>
+  <x:si>
     <x:t>85,00% CDI</x:t>
   </x:si>
   <x:si>
-    <x:t>1.014.233,00</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 1.602.489,13</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 1.617.331,25</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 1.613.991,77</x:t>
-  </x:si>
-  <x:si>
-    <x:t>510.332,00</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 801.221,46</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 808.642,30</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 806.972,61</x:t>
-  </x:si>
-  <x:si>
-    <x:t>08/09/2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>09/10/2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>628.930,00</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 1.000.000,00</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 1.002.637,55</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 1.002.044,10</x:t>
-  </x:si>
-  <x:si>
-    <x:t>52,9%|Fundos de Investimento</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 5.017.170,75</x:t>
-  </x:si>
-  <x:si>
-    <x:t>52,80%|Fundos de Renda Fixa Pós-Fixado</x:t>
+    <x:t>141.103,00</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 225.765,23</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 225.840,76</x:t>
+  </x:si>
+  <x:si>
+    <x:t>70,4%|Fundos de Investimento</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 5.836.424,41</x:t>
+  </x:si>
+  <x:si>
+    <x:t>70,30%|Fundos de Renda Fixa Pós-Fixado</x:t>
   </x:si>
   <x:si>
     <x:t>Data cota</x:t>
@@ -178,10 +175,10 @@
     <x:t>XP Bancos FIRF Referenciada DI CP RL</x:t>
   </x:si>
   <x:si>
-    <x:t>15/09/2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 1,94</x:t>
+    <x:t>21/09/2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 1,95</x:t>
   </x:si>
   <x:si>
     <x:t>772.979,35</x:t>
@@ -190,58 +187,73 @@
     <x:t>R$ 0,00</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 1.500.781,15</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 1.500.024,21</x:t>
+    <x:t>R$ 1.503.943,96</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 1.500.733,58</x:t>
+  </x:si>
+  <x:si>
+    <x:t>XP Bancos FIC de FIRF Referenciado DI CP - RL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 1,54</x:t>
+  </x:si>
+  <x:si>
+    <x:t>526.379,08</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 808.843,61</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 808.091,53</x:t>
   </x:si>
   <x:si>
     <x:t>Bradesco SKY FIC FIRF Referenciada DI RL</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 1.451,45</x:t>
+    <x:t>R$ 1.454,48</x:t>
   </x:si>
   <x:si>
     <x:t>1.188,48</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 1.725.011,61</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 1.722.655,31</x:t>
+    <x:t>R$ 1.728.616,07</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 1.724.226,37</x:t>
   </x:si>
   <x:si>
     <x:t>Bradesco Bancos II FIF CIC RF CP RL</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 1,48</x:t>
+    <x:t>R$ 1,49</x:t>
   </x:si>
   <x:si>
     <x:t>353.356,60</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 524.029,25</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 518.818,37</x:t>
+    <x:t>R$ 525.137,38</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 519.677,17</x:t>
   </x:si>
   <x:si>
     <x:t>Safra Extra Bancos Special FIC FIRF CP</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 142,42</x:t>
+    <x:t>R$ 142,71</x:t>
   </x:si>
   <x:si>
     <x:t>8.898,52</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 1.267.348,74</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 1.258.539,80</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 222,42</x:t>
+    <x:t>R$ 1.269.883,39</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 1.260.504,15</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 1,84</x:t>
   </x:si>
   <x:si>
     <x:t>Resgate de fundo pendente</x:t>
@@ -271,7 +283,7 @@
     <x:t>Saldo Projetado  (D &gt; 3)</x:t>
   </x:si>
   <x:si>
-    <x:t>222,42</x:t>
+    <x:t>1,84</x:t>
   </x:si>
   <x:si>
     <x:t>0</x:t>
@@ -516,11 +528,11 @@
       <x:alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="1" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
+    <x:xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="1" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
     <x:xf numFmtId="0" fontId="3" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="1" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="1" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
@@ -879,13 +891,13 @@
     </x:row>
     <x:row r="4" spans="1:11" ht="30" customHeight="1">
       <x:c r="A4" s="6">
-        <x:v>9484917.92591729</x:v>
+        <x:v>8295092.66885763</x:v>
       </x:c>
       <x:c r="B4" s="7">
-        <x:v>9484695.50591729</x:v>
+        <x:v>8295090.82885763</x:v>
       </x:c>
       <x:c r="C4" s="7">
-        <x:v>222.42</x:v>
+        <x:v>1.84</x:v>
       </x:c>
       <x:c r="D4" s="7">
         <x:v>0</x:v>
@@ -1013,240 +1025,242 @@
         <x:v>25</x:v>
       </x:c>
       <x:c r="I10" s="12" t="s">
-        <x:v>7</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="J10" s="12" t="s">
-        <x:v>7</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="K10" s="3"/>
     </x:row>
-    <x:row r="11" spans="1:11">
-      <x:c r="A11" s="4"/>
-      <x:c r="B11" s="4"/>
-      <x:c r="C11" s="4"/>
-      <x:c r="D11" s="4"/>
-      <x:c r="E11" s="4"/>
-      <x:c r="F11" s="4"/>
-      <x:c r="G11" s="4"/>
-      <x:c r="H11" s="4"/>
-      <x:c r="I11" s="4"/>
-      <x:c r="J11" s="4"/>
-      <x:c r="K11" s="4"/>
-    </x:row>
-    <x:row r="12" spans="1:11" ht="45" customHeight="1">
-      <x:c r="A12" s="8" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="B12" s="9"/>
-      <x:c r="C12" s="9"/>
-      <x:c r="D12" s="9"/>
-      <x:c r="E12" s="9"/>
-      <x:c r="F12" s="9"/>
-      <x:c r="G12" s="10" t="s">
+    <x:row r="11" spans="1:11" ht="30" customHeight="1">
+      <x:c r="A11" s="13" t="s">
         <x:v>27</x:v>
       </x:c>
-      <x:c r="H12" s="3"/>
-      <x:c r="I12" s="3"/>
-      <x:c r="J12" s="3"/>
-      <x:c r="K12" s="3"/>
-    </x:row>
-    <x:row r="13" spans="1:11">
-      <x:c r="A13" s="4"/>
-      <x:c r="B13" s="4"/>
-      <x:c r="C13" s="4"/>
-      <x:c r="D13" s="4"/>
-      <x:c r="E13" s="4"/>
-      <x:c r="F13" s="4"/>
-      <x:c r="G13" s="4"/>
+      <x:c r="B11" s="13" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="C11" s="13" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="D11" s="13" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="E11" s="13" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="F11" s="13" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="G11" s="13" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="H11" s="13" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="I11" s="13" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="J11" s="13" t="s">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="K11" s="3"/>
+    </x:row>
+    <x:row r="12" spans="1:11">
+      <x:c r="A12" s="4"/>
+      <x:c r="B12" s="4"/>
+      <x:c r="C12" s="4"/>
+      <x:c r="D12" s="4"/>
+      <x:c r="E12" s="4"/>
+      <x:c r="F12" s="4"/>
+      <x:c r="G12" s="4"/>
+      <x:c r="H12" s="4"/>
+      <x:c r="I12" s="4"/>
+      <x:c r="J12" s="4"/>
+      <x:c r="K12" s="4"/>
+    </x:row>
+    <x:row r="13" spans="1:11" ht="45" customHeight="1">
+      <x:c r="A13" s="8" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="B13" s="9"/>
+      <x:c r="C13" s="9"/>
+      <x:c r="D13" s="9"/>
+      <x:c r="E13" s="9"/>
+      <x:c r="F13" s="9"/>
+      <x:c r="G13" s="10" t="s">
+        <x:v>37</x:v>
+      </x:c>
       <x:c r="H13" s="3"/>
       <x:c r="I13" s="3"/>
       <x:c r="J13" s="3"/>
       <x:c r="K13" s="3"/>
     </x:row>
-    <x:row r="14" spans="1:11" ht="35.1" customHeight="1">
-      <x:c r="A14" s="11" t="s">
-        <x:v>28</x:v>
-      </x:c>
-      <x:c r="B14" s="11" t="s">
+    <x:row r="14" spans="1:11">
+      <x:c r="A14" s="4"/>
+      <x:c r="B14" s="4"/>
+      <x:c r="C14" s="4"/>
+      <x:c r="D14" s="4"/>
+      <x:c r="E14" s="4"/>
+      <x:c r="F14" s="4"/>
+      <x:c r="G14" s="4"/>
+      <x:c r="H14" s="3"/>
+      <x:c r="I14" s="3"/>
+      <x:c r="J14" s="3"/>
+      <x:c r="K14" s="3"/>
+    </x:row>
+    <x:row r="15" spans="1:11" ht="35.1" customHeight="1">
+      <x:c r="A15" s="11" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="B15" s="11" t="s">
         <x:v>9</x:v>
       </x:c>
-      <x:c r="C14" s="11" t="s">
+      <x:c r="C15" s="11" t="s">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="D14" s="11" t="s">
+      <x:c r="D15" s="11" t="s">
         <x:v>11</x:v>
       </x:c>
-      <x:c r="E14" s="11" t="s">
+      <x:c r="E15" s="11" t="s">
         <x:v>12</x:v>
       </x:c>
-      <x:c r="F14" s="11" t="s">
+      <x:c r="F15" s="11" t="s">
         <x:v>13</x:v>
       </x:c>
-      <x:c r="G14" s="11" t="s">
+      <x:c r="G15" s="11" t="s">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="H14" s="11" t="s">
+      <x:c r="H15" s="11" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="I14" s="11" t="s">
+      <x:c r="I15" s="11" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="J14" s="11" t="s">
+      <x:c r="J15" s="11" t="s">
         <x:v>17</x:v>
-      </x:c>
-      <x:c r="K14" s="3"/>
-    </x:row>
-    <x:row r="15" spans="1:11" ht="30" customHeight="1">
-      <x:c r="A15" s="13"/>
-      <x:c r="B15" s="13" t="s">
-        <x:v>29</x:v>
-      </x:c>
-      <x:c r="C15" s="13"/>
-      <x:c r="D15" s="13" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="E15" s="13" t="s">
-        <x:v>31</x:v>
-      </x:c>
-      <x:c r="F15" s="13" t="s">
-        <x:v>32</x:v>
-      </x:c>
-      <x:c r="G15" s="13" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="H15" s="13" t="s">
-        <x:v>33</x:v>
-      </x:c>
-      <x:c r="I15" s="13" t="s">
-        <x:v>34</x:v>
-      </x:c>
-      <x:c r="J15" s="13" t="s">
-        <x:v>35</x:v>
       </x:c>
       <x:c r="K15" s="3"/>
     </x:row>
     <x:row r="16" spans="1:11" ht="30" customHeight="1">
       <x:c r="A16" s="13"/>
       <x:c r="B16" s="13" t="s">
-        <x:v>29</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="C16" s="13"/>
       <x:c r="D16" s="13" t="s">
-        <x:v>30</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="E16" s="13" t="s">
-        <x:v>31</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="F16" s="13" t="s">
-        <x:v>36</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="G16" s="13" t="s">
         <x:v>24</x:v>
       </x:c>
       <x:c r="H16" s="13" t="s">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="I16" s="13" t="s">
         <x:v>37</x:v>
       </x:c>
-      <x:c r="I16" s="13" t="s">
-        <x:v>38</x:v>
-      </x:c>
       <x:c r="J16" s="13" t="s">
-        <x:v>39</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="K16" s="3"/>
     </x:row>
-    <x:row r="17" spans="1:11" ht="30" customHeight="1">
-      <x:c r="A17" s="12"/>
-      <x:c r="B17" s="12" t="s">
-        <x:v>40</x:v>
-      </x:c>
-      <x:c r="C17" s="12"/>
-      <x:c r="D17" s="12" t="s">
-        <x:v>41</x:v>
-      </x:c>
-      <x:c r="E17" s="12" t="s">
-        <x:v>31</x:v>
-      </x:c>
-      <x:c r="F17" s="12" t="s">
-        <x:v>42</x:v>
-      </x:c>
-      <x:c r="G17" s="12" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="H17" s="12" t="s">
-        <x:v>43</x:v>
-      </x:c>
-      <x:c r="I17" s="12" t="s">
-        <x:v>44</x:v>
-      </x:c>
-      <x:c r="J17" s="12" t="s">
+    <x:row r="17" spans="1:11">
+      <x:c r="A17" s="4"/>
+      <x:c r="B17" s="4"/>
+      <x:c r="C17" s="4"/>
+      <x:c r="D17" s="4"/>
+      <x:c r="E17" s="4"/>
+      <x:c r="F17" s="4"/>
+      <x:c r="G17" s="4"/>
+      <x:c r="H17" s="4"/>
+      <x:c r="I17" s="4"/>
+      <x:c r="J17" s="4"/>
+      <x:c r="K17" s="4"/>
+    </x:row>
+    <x:row r="18" spans="1:11" ht="45" customHeight="1">
+      <x:c r="A18" s="8" t="s">
         <x:v>45</x:v>
       </x:c>
-      <x:c r="K17" s="3"/>
-    </x:row>
-    <x:row r="18" spans="1:11">
-      <x:c r="A18" s="4"/>
-      <x:c r="B18" s="4"/>
-      <x:c r="C18" s="4"/>
-      <x:c r="D18" s="4"/>
-      <x:c r="E18" s="4"/>
-      <x:c r="F18" s="4"/>
-      <x:c r="G18" s="4"/>
-      <x:c r="H18" s="4"/>
-      <x:c r="I18" s="4"/>
-      <x:c r="J18" s="4"/>
-      <x:c r="K18" s="4"/>
-    </x:row>
-    <x:row r="19" spans="1:11" ht="45" customHeight="1">
-      <x:c r="A19" s="8" t="s">
+      <x:c r="B18" s="9"/>
+      <x:c r="C18" s="9"/>
+      <x:c r="D18" s="9"/>
+      <x:c r="E18" s="9"/>
+      <x:c r="F18" s="9"/>
+      <x:c r="G18" s="10" t="s">
         <x:v>46</x:v>
       </x:c>
-      <x:c r="B19" s="9"/>
-      <x:c r="C19" s="9"/>
-      <x:c r="D19" s="9"/>
-      <x:c r="E19" s="9"/>
-      <x:c r="F19" s="9"/>
-      <x:c r="G19" s="10" t="s">
-        <x:v>47</x:v>
-      </x:c>
+      <x:c r="H18" s="3"/>
+      <x:c r="I18" s="3"/>
+      <x:c r="J18" s="3"/>
+      <x:c r="K18" s="3"/>
+    </x:row>
+    <x:row r="19" spans="1:11">
+      <x:c r="A19" s="4"/>
+      <x:c r="B19" s="4"/>
+      <x:c r="C19" s="4"/>
+      <x:c r="D19" s="4"/>
+      <x:c r="E19" s="4"/>
+      <x:c r="F19" s="4"/>
+      <x:c r="G19" s="4"/>
       <x:c r="H19" s="3"/>
       <x:c r="I19" s="3"/>
       <x:c r="J19" s="3"/>
       <x:c r="K19" s="3"/>
     </x:row>
-    <x:row r="20" spans="1:11">
-      <x:c r="A20" s="4"/>
-      <x:c r="B20" s="4"/>
-      <x:c r="C20" s="4"/>
-      <x:c r="D20" s="4"/>
-      <x:c r="E20" s="4"/>
-      <x:c r="F20" s="4"/>
-      <x:c r="G20" s="4"/>
+    <x:row r="20" spans="1:11" ht="35.1" customHeight="1">
+      <x:c r="A20" s="11" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="B20" s="11" t="s">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="C20" s="11" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="D20" s="11" t="s">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="E20" s="11" t="s">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="F20" s="11" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="G20" s="11" t="s">
+        <x:v>17</x:v>
+      </x:c>
       <x:c r="H20" s="3"/>
       <x:c r="I20" s="3"/>
       <x:c r="J20" s="3"/>
       <x:c r="K20" s="3"/>
     </x:row>
-    <x:row r="21" spans="1:11" ht="35.1" customHeight="1">
-      <x:c r="A21" s="11" t="s">
-        <x:v>48</x:v>
-      </x:c>
-      <x:c r="B21" s="11" t="s">
-        <x:v>49</x:v>
-      </x:c>
-      <x:c r="C21" s="11" t="s">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="D21" s="11" t="s">
-        <x:v>51</x:v>
-      </x:c>
-      <x:c r="E21" s="11" t="s">
+    <x:row r="21" spans="1:11" ht="30" customHeight="1">
+      <x:c r="A21" s="12" t="s">
         <x:v>52</x:v>
       </x:c>
-      <x:c r="F21" s="11" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="G21" s="11" t="s">
-        <x:v>17</x:v>
+      <x:c r="B21" s="12" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="C21" s="12" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="D21" s="12" t="s">
+        <x:v>55</x:v>
+      </x:c>
+      <x:c r="E21" s="12" t="s">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="F21" s="12" t="s">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="G21" s="12" t="s">
+        <x:v>58</x:v>
       </x:c>
       <x:c r="H21" s="3"/>
       <x:c r="I21" s="3"/>
@@ -1254,26 +1268,26 @@
       <x:c r="K21" s="3"/>
     </x:row>
     <x:row r="22" spans="1:11" ht="30" customHeight="1">
-      <x:c r="A22" s="13" t="s">
+      <x:c r="A22" s="12" t="s">
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="B22" s="12" t="s">
         <x:v>53</x:v>
       </x:c>
-      <x:c r="B22" s="13" t="s">
-        <x:v>54</x:v>
-      </x:c>
-      <x:c r="C22" s="13" t="s">
-        <x:v>55</x:v>
-      </x:c>
-      <x:c r="D22" s="13" t="s">
+      <x:c r="C22" s="12" t="s">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="D22" s="12" t="s">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="E22" s="12" t="s">
         <x:v>56</x:v>
       </x:c>
-      <x:c r="E22" s="13" t="s">
-        <x:v>57</x:v>
-      </x:c>
-      <x:c r="F22" s="13" t="s">
-        <x:v>58</x:v>
-      </x:c>
-      <x:c r="G22" s="13" t="s">
-        <x:v>59</x:v>
+      <x:c r="F22" s="12" t="s">
+        <x:v>62</x:v>
+      </x:c>
+      <x:c r="G22" s="12" t="s">
+        <x:v>63</x:v>
       </x:c>
       <x:c r="H22" s="3"/>
       <x:c r="I22" s="3"/>
@@ -1281,26 +1295,26 @@
       <x:c r="K22" s="3"/>
     </x:row>
     <x:row r="23" spans="1:11" ht="30" customHeight="1">
-      <x:c r="A23" s="13" t="s">
-        <x:v>60</x:v>
-      </x:c>
-      <x:c r="B23" s="13" t="s">
-        <x:v>54</x:v>
-      </x:c>
-      <x:c r="C23" s="13" t="s">
-        <x:v>61</x:v>
-      </x:c>
-      <x:c r="D23" s="13" t="s">
-        <x:v>62</x:v>
-      </x:c>
-      <x:c r="E23" s="13" t="s">
-        <x:v>57</x:v>
-      </x:c>
-      <x:c r="F23" s="13" t="s">
-        <x:v>63</x:v>
-      </x:c>
-      <x:c r="G23" s="13" t="s">
+      <x:c r="A23" s="12" t="s">
         <x:v>64</x:v>
+      </x:c>
+      <x:c r="B23" s="12" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="C23" s="12" t="s">
+        <x:v>65</x:v>
+      </x:c>
+      <x:c r="D23" s="12" t="s">
+        <x:v>66</x:v>
+      </x:c>
+      <x:c r="E23" s="12" t="s">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="F23" s="12" t="s">
+        <x:v>67</x:v>
+      </x:c>
+      <x:c r="G23" s="12" t="s">
+        <x:v>68</x:v>
       </x:c>
       <x:c r="H23" s="3"/>
       <x:c r="I23" s="3"/>
@@ -1308,26 +1322,26 @@
       <x:c r="K23" s="3"/>
     </x:row>
     <x:row r="24" spans="1:11" ht="30" customHeight="1">
-      <x:c r="A24" s="13" t="s">
-        <x:v>65</x:v>
-      </x:c>
-      <x:c r="B24" s="13" t="s">
-        <x:v>54</x:v>
-      </x:c>
-      <x:c r="C24" s="13" t="s">
-        <x:v>66</x:v>
-      </x:c>
-      <x:c r="D24" s="13" t="s">
-        <x:v>67</x:v>
-      </x:c>
-      <x:c r="E24" s="13" t="s">
-        <x:v>57</x:v>
-      </x:c>
-      <x:c r="F24" s="13" t="s">
-        <x:v>68</x:v>
-      </x:c>
-      <x:c r="G24" s="13" t="s">
+      <x:c r="A24" s="12" t="s">
         <x:v>69</x:v>
+      </x:c>
+      <x:c r="B24" s="12" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="C24" s="12" t="s">
+        <x:v>70</x:v>
+      </x:c>
+      <x:c r="D24" s="12" t="s">
+        <x:v>71</x:v>
+      </x:c>
+      <x:c r="E24" s="12" t="s">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="F24" s="12" t="s">
+        <x:v>72</x:v>
+      </x:c>
+      <x:c r="G24" s="12" t="s">
+        <x:v>73</x:v>
       </x:c>
       <x:c r="H24" s="3"/>
       <x:c r="I24" s="3"/>
@@ -1335,26 +1349,26 @@
       <x:c r="K24" s="3"/>
     </x:row>
     <x:row r="25" spans="1:11" ht="30" customHeight="1">
-      <x:c r="A25" s="12" t="s">
-        <x:v>70</x:v>
-      </x:c>
-      <x:c r="B25" s="12" t="s">
-        <x:v>54</x:v>
-      </x:c>
-      <x:c r="C25" s="12" t="s">
-        <x:v>71</x:v>
-      </x:c>
-      <x:c r="D25" s="12" t="s">
-        <x:v>72</x:v>
-      </x:c>
-      <x:c r="E25" s="12" t="s">
-        <x:v>57</x:v>
-      </x:c>
-      <x:c r="F25" s="12" t="s">
-        <x:v>73</x:v>
-      </x:c>
-      <x:c r="G25" s="12" t="s">
+      <x:c r="A25" s="13" t="s">
         <x:v>74</x:v>
+      </x:c>
+      <x:c r="B25" s="13" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="C25" s="13" t="s">
+        <x:v>75</x:v>
+      </x:c>
+      <x:c r="D25" s="13" t="s">
+        <x:v>76</x:v>
+      </x:c>
+      <x:c r="E25" s="13" t="s">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="F25" s="13" t="s">
+        <x:v>77</x:v>
+      </x:c>
+      <x:c r="G25" s="13" t="s">
+        <x:v>78</x:v>
       </x:c>
       <x:c r="H25" s="3"/>
       <x:c r="I25" s="3"/>
@@ -1388,7 +1402,7 @@
       <x:c r="I27" s="9"/>
       <x:c r="J27" s="9"/>
       <x:c r="K27" s="10" t="s">
-        <x:v>75</x:v>
+        <x:v>79</x:v>
       </x:c>
     </x:row>
     <x:row r="28" spans="1:11">
@@ -1412,66 +1426,66 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="C29" s="11" t="s">
-        <x:v>76</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="D29" s="11" t="s">
-        <x:v>77</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="E29" s="11" t="s">
-        <x:v>78</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="F29" s="11" t="s">
-        <x:v>79</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="G29" s="11" t="s">
-        <x:v>80</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="H29" s="11" t="s">
-        <x:v>81</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="I29" s="11" t="s">
-        <x:v>82</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="J29" s="11" t="s">
-        <x:v>83</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="K29" s="11" t="s">
-        <x:v>84</x:v>
+        <x:v>88</x:v>
       </x:c>
     </x:row>
     <x:row r="30" spans="1:11" ht="30" customHeight="1">
-      <x:c r="A30" s="12" t="s">
-        <x:v>85</x:v>
-      </x:c>
-      <x:c r="B30" s="12" t="s">
-        <x:v>86</x:v>
-      </x:c>
-      <x:c r="C30" s="12" t="s">
-        <x:v>86</x:v>
-      </x:c>
-      <x:c r="D30" s="12" t="s">
-        <x:v>86</x:v>
-      </x:c>
-      <x:c r="E30" s="12" t="s">
-        <x:v>86</x:v>
-      </x:c>
-      <x:c r="F30" s="12" t="s">
-        <x:v>86</x:v>
-      </x:c>
-      <x:c r="G30" s="12" t="s">
-        <x:v>86</x:v>
-      </x:c>
-      <x:c r="H30" s="12" t="s">
-        <x:v>86</x:v>
-      </x:c>
-      <x:c r="I30" s="12" t="s">
-        <x:v>86</x:v>
-      </x:c>
-      <x:c r="J30" s="12" t="s">
-        <x:v>86</x:v>
-      </x:c>
-      <x:c r="K30" s="12" t="s">
-        <x:v>86</x:v>
+      <x:c r="A30" s="13" t="s">
+        <x:v>89</x:v>
+      </x:c>
+      <x:c r="B30" s="13" t="s">
+        <x:v>90</x:v>
+      </x:c>
+      <x:c r="C30" s="13" t="s">
+        <x:v>90</x:v>
+      </x:c>
+      <x:c r="D30" s="13" t="s">
+        <x:v>90</x:v>
+      </x:c>
+      <x:c r="E30" s="13" t="s">
+        <x:v>90</x:v>
+      </x:c>
+      <x:c r="F30" s="13" t="s">
+        <x:v>90</x:v>
+      </x:c>
+      <x:c r="G30" s="13" t="s">
+        <x:v>90</x:v>
+      </x:c>
+      <x:c r="H30" s="13" t="s">
+        <x:v>90</x:v>
+      </x:c>
+      <x:c r="I30" s="13" t="s">
+        <x:v>90</x:v>
+      </x:c>
+      <x:c r="J30" s="13" t="s">
+        <x:v>90</x:v>
+      </x:c>
+      <x:c r="K30" s="13" t="s">
+        <x:v>90</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -1479,8 +1493,8 @@
     <x:mergeCell ref="A1:E1"/>
     <x:mergeCell ref="F1:G1"/>
     <x:mergeCell ref="A7:F7"/>
-    <x:mergeCell ref="A12:F12"/>
-    <x:mergeCell ref="A19:F19"/>
+    <x:mergeCell ref="A13:F13"/>
+    <x:mergeCell ref="A18:F18"/>
     <x:mergeCell ref="A27:J27"/>
   </x:mergeCells>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>

--- a/data/positions/Posição Consolidada - 7983962.xlsx
+++ b/data/positions/Posição Consolidada - 7983962.xlsx
@@ -19,7 +19,7 @@
     <x:t>XP</x:t>
   </x:si>
   <x:si>
-    <x:t>Conta: 7983962 | 21/09/2026, 16:40</x:t>
+    <x:t>Conta: 7983962 | 23/09/2026, 09:37</x:t>
   </x:si>
   <x:si>
     <x:t>Este é o seu patrimônio</x:t>
@@ -37,7 +37,7 @@
     <x:t>26,9%|Renda Fixa</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 2.232.803,73</x:t>
+    <x:t>R$ 2.234.732,71</x:t>
   </x:si>
   <x:si>
     <x:t>26,90%|Pós-Fixada</x:t>
@@ -94,7 +94,7 @@
     <x:t>R$ 1.000.949,68</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 1.040.259,47</x:t>
+    <x:t>R$ 1.041.152,53</x:t>
   </x:si>
   <x:si>
     <x:t>LCI CEF - MAI/2027</x:t>
@@ -118,16 +118,16 @@
     <x:t>R$ 1.191.509,24</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 1.192.544,26</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 1.191.654,14</x:t>
+    <x:t>R$ 1.193.580,18</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 1.191.923,43</x:t>
   </x:si>
   <x:si>
     <x:t>2,72%|Operações Compromissadas</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 225.862,69</x:t>
+    <x:t>R$ 226.057,74</x:t>
   </x:si>
   <x:si>
     <x:t>2,70%|Pós-Fixada</x:t>
@@ -148,13 +148,13 @@
     <x:t>R$ 225.765,23</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 225.840,76</x:t>
+    <x:t>R$ 225.991,92</x:t>
   </x:si>
   <x:si>
     <x:t>70,4%|Fundos de Investimento</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 5.836.424,41</x:t>
+    <x:t>R$ 5.841.501,89</x:t>
   </x:si>
   <x:si>
     <x:t>70,30%|Fundos de Renda Fixa Pós-Fixado</x:t>
@@ -175,7 +175,7 @@
     <x:t>XP Bancos FIRF Referenciada DI CP RL</x:t>
   </x:si>
   <x:si>
-    <x:t>21/09/2026</x:t>
+    <x:t>23/09/2026</x:t>
   </x:si>
   <x:si>
     <x:t>R$ 1,95</x:t>
@@ -187,10 +187,10 @@
     <x:t>R$ 0,00</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 1.503.943,96</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 1.500.733,58</x:t>
+    <x:t>R$ 1.505.419,28</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 1.501.259,98</x:t>
   </x:si>
   <x:si>
     <x:t>XP Bancos FIC de FIRF Referenciado DI CP - RL</x:t>
@@ -202,25 +202,25 @@
     <x:t>526.379,08</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 808.843,61</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 808.091,53</x:t>
+    <x:t>R$ 809.621,63</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 808.251,35</x:t>
   </x:si>
   <x:si>
     <x:t>Bradesco SKY FIC FIRF Referenciada DI RL</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 1.454,48</x:t>
+    <x:t>R$ 1.455,89</x:t>
   </x:si>
   <x:si>
     <x:t>1.188,48</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 1.728.616,07</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 1.724.226,37</x:t>
+    <x:t>R$ 1.730.285,54</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 1.725.156,30</x:t>
   </x:si>
   <x:si>
     <x:t>Bradesco Bancos II FIF CIC RF CP RL</x:t>
@@ -232,25 +232,28 @@
     <x:t>353.356,60</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 525.137,38</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 519.677,17</x:t>
+    <x:t>R$ 525.676,17</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 520.094,74</x:t>
   </x:si>
   <x:si>
     <x:t>Safra Extra Bancos Special FIC FIRF CP</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 142,71</x:t>
+    <x:t>22/09/2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 142,78</x:t>
   </x:si>
   <x:si>
     <x:t>8.898,52</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 1.269.883,39</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 1.260.504,15</x:t>
+    <x:t>R$ 1.270.499,27</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 1.260.981,45</x:t>
   </x:si>
   <x:si>
     <x:t>R$ 1,84</x:t>
@@ -891,10 +894,10 @@
     </x:row>
     <x:row r="4" spans="1:11" ht="30" customHeight="1">
       <x:c r="A4" s="6">
-        <x:v>8295092.66885763</x:v>
+        <x:v>8302294.18346435</x:v>
       </x:c>
       <x:c r="B4" s="7">
-        <x:v>8295090.82885763</x:v>
+        <x:v>8302292.34346435</x:v>
       </x:c>
       <x:c r="C4" s="7">
         <x:v>1.84</x:v>
@@ -1353,22 +1356,22 @@
         <x:v>74</x:v>
       </x:c>
       <x:c r="B25" s="13" t="s">
-        <x:v>53</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="C25" s="13" t="s">
-        <x:v>75</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="D25" s="13" t="s">
-        <x:v>76</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="E25" s="13" t="s">
         <x:v>56</x:v>
       </x:c>
       <x:c r="F25" s="13" t="s">
-        <x:v>77</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="G25" s="13" t="s">
-        <x:v>78</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="H25" s="3"/>
       <x:c r="I25" s="3"/>
@@ -1402,7 +1405,7 @@
       <x:c r="I27" s="9"/>
       <x:c r="J27" s="9"/>
       <x:c r="K27" s="10" t="s">
-        <x:v>79</x:v>
+        <x:v>80</x:v>
       </x:c>
     </x:row>
     <x:row r="28" spans="1:11">
@@ -1426,66 +1429,66 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="C29" s="11" t="s">
-        <x:v>80</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="D29" s="11" t="s">
-        <x:v>81</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="E29" s="11" t="s">
-        <x:v>82</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="F29" s="11" t="s">
-        <x:v>83</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="G29" s="11" t="s">
-        <x:v>84</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="H29" s="11" t="s">
-        <x:v>85</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="I29" s="11" t="s">
-        <x:v>86</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="J29" s="11" t="s">
-        <x:v>87</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="K29" s="11" t="s">
-        <x:v>88</x:v>
+        <x:v>89</x:v>
       </x:c>
     </x:row>
     <x:row r="30" spans="1:11" ht="30" customHeight="1">
       <x:c r="A30" s="13" t="s">
-        <x:v>89</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="B30" s="13" t="s">
-        <x:v>90</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="C30" s="13" t="s">
-        <x:v>90</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="D30" s="13" t="s">
-        <x:v>90</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="E30" s="13" t="s">
-        <x:v>90</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="F30" s="13" t="s">
-        <x:v>90</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="G30" s="13" t="s">
-        <x:v>90</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="H30" s="13" t="s">
-        <x:v>90</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="I30" s="13" t="s">
-        <x:v>90</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="J30" s="13" t="s">
-        <x:v>90</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="K30" s="13" t="s">
-        <x:v>90</x:v>
+        <x:v>91</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/data/positions/Posição Consolidada - 7983962.xlsx
+++ b/data/positions/Posição Consolidada - 7983962.xlsx
@@ -19,7 +19,7 @@
     <x:t>XP</x:t>
   </x:si>
   <x:si>
-    <x:t>Conta: 7983962 | 23/09/2026, 09:37</x:t>
+    <x:t>Conta: 7983962 | 30/09/2026, 08:51</x:t>
   </x:si>
   <x:si>
     <x:t>Este é o seu patrimônio</x:t>
@@ -34,13 +34,13 @@
     <x:t>Saldo projetado</x:t>
   </x:si>
   <x:si>
-    <x:t>26,9%|Renda Fixa</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 2.234.732,71</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26,90%|Pós-Fixada</x:t>
+    <x:t>20,8%|Renda Fixa</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 2.239.562,47</x:t>
+  </x:si>
+  <x:si>
+    <x:t>20,70%|Pós-Fixada</x:t>
   </x:si>
   <x:si>
     <x:t>Aplicação</x:t>
@@ -94,7 +94,7 @@
     <x:t>R$ 1.000.949,68</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 1.041.152,53</x:t>
+    <x:t>R$ 1.043.388,55</x:t>
   </x:si>
   <x:si>
     <x:t>LCI CEF - MAI/2027</x:t>
@@ -118,46 +118,46 @@
     <x:t>R$ 1.191.509,24</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 1.193.580,18</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 1.191.923,43</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2,72%|Operações Compromissadas</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 226.057,74</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2,70%|Pós-Fixada</x:t>
-  </x:si>
-  <x:si>
-    <x:t>18/09/2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>22/10/2026</x:t>
+    <x:t>R$ 1.196.173,92</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 1.193.561,70</x:t>
+  </x:si>
+  <x:si>
+    <x:t>24,9%|Operações Compromissadas</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 2.682.256,81</x:t>
+  </x:si>
+  <x:si>
+    <x:t>24,80%|Pós-Fixada</x:t>
+  </x:si>
+  <x:si>
+    <x:t>23/09/2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>27/10/2026</x:t>
   </x:si>
   <x:si>
     <x:t>85,00% CDI</x:t>
   </x:si>
   <x:si>
-    <x:t>141.103,00</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 225.765,23</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 225.991,92</x:t>
-  </x:si>
-  <x:si>
-    <x:t>70,4%|Fundos de Investimento</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 5.841.501,89</x:t>
-  </x:si>
-  <x:si>
-    <x:t>70,30%|Fundos de Renda Fixa Pós-Fixado</x:t>
+    <x:t>1.683.317,00</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 2.676.474,67</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 2.680.955,83</x:t>
+  </x:si>
+  <x:si>
+    <x:t>54,3%|Fundos de Investimento</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 5.854.883,81</x:t>
+  </x:si>
+  <x:si>
+    <x:t>54,30%|Fundos de Renda Fixa Pós-Fixado</x:t>
   </x:si>
   <x:si>
     <x:t>Data cota</x:t>
@@ -175,7 +175,7 @@
     <x:t>XP Bancos FIRF Referenciada DI CP RL</x:t>
   </x:si>
   <x:si>
-    <x:t>23/09/2026</x:t>
+    <x:t>29/09/2026</x:t>
   </x:si>
   <x:si>
     <x:t>R$ 1,95</x:t>
@@ -187,10 +187,10 @@
     <x:t>R$ 0,00</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 1.505.419,28</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 1.501.259,98</x:t>
+    <x:t>R$ 1.508.572,08</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 1.503.321,68</x:t>
   </x:si>
   <x:si>
     <x:t>XP Bancos FIC de FIRF Referenciado DI CP - RL</x:t>
@@ -202,25 +202,28 @@
     <x:t>526.379,08</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 809.621,63</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 808.251,35</x:t>
+    <x:t>R$ 811.285,57</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 809.018,53</x:t>
   </x:si>
   <x:si>
     <x:t>Bradesco SKY FIC FIRF Referenciada DI RL</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 1.455,89</x:t>
+    <x:t>30/09/2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 1.459,43</x:t>
   </x:si>
   <x:si>
     <x:t>1.188,48</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 1.730.285,54</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 1.725.156,30</x:t>
+    <x:t>R$ 1.734.500,59</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 1.728.907,73</x:t>
   </x:si>
   <x:si>
     <x:t>Bradesco Bancos II FIF CIC RF CP RL</x:t>
@@ -232,31 +235,28 @@
     <x:t>353.356,60</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 525.676,17</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 520.094,74</x:t>
+    <x:t>R$ 527.018,58</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 521.135,10</x:t>
   </x:si>
   <x:si>
     <x:t>Safra Extra Bancos Special FIC FIRF CP</x:t>
   </x:si>
   <x:si>
-    <x:t>22/09/2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 142,78</x:t>
+    <x:t>R$ 143,11</x:t>
   </x:si>
   <x:si>
     <x:t>8.898,52</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 1.270.499,27</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 1.260.981,45</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 1,84</x:t>
+    <x:t>R$ 1.273.506,99</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 1.263.312,44</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 4,04</x:t>
   </x:si>
   <x:si>
     <x:t>Resgate de fundo pendente</x:t>
@@ -286,7 +286,7 @@
     <x:t>Saldo Projetado  (D &gt; 3)</x:t>
   </x:si>
   <x:si>
-    <x:t>1,84</x:t>
+    <x:t>4,04</x:t>
   </x:si>
   <x:si>
     <x:t>0</x:t>
@@ -894,13 +894,13 @@
     </x:row>
     <x:row r="4" spans="1:11" ht="30" customHeight="1">
       <x:c r="A4" s="6">
-        <x:v>8302294.18346435</x:v>
+        <x:v>10776707.1304028</x:v>
       </x:c>
       <x:c r="B4" s="7">
-        <x:v>8302292.34346435</x:v>
+        <x:v>10776703.0904028</x:v>
       </x:c>
       <x:c r="C4" s="7">
-        <x:v>1.84</x:v>
+        <x:v>4.04</x:v>
       </x:c>
       <x:c r="D4" s="7">
         <x:v>0</x:v>
@@ -1302,22 +1302,22 @@
         <x:v>64</x:v>
       </x:c>
       <x:c r="B23" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="C23" s="12" t="s">
-        <x:v>65</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="D23" s="12" t="s">
-        <x:v>66</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="E23" s="12" t="s">
         <x:v>56</x:v>
       </x:c>
       <x:c r="F23" s="12" t="s">
-        <x:v>67</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="G23" s="12" t="s">
-        <x:v>68</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="H23" s="3"/>
       <x:c r="I23" s="3"/>
@@ -1326,25 +1326,25 @@
     </x:row>
     <x:row r="24" spans="1:11" ht="30" customHeight="1">
       <x:c r="A24" s="12" t="s">
-        <x:v>69</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="B24" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="C24" s="12" t="s">
-        <x:v>70</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="D24" s="12" t="s">
-        <x:v>71</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="E24" s="12" t="s">
         <x:v>56</x:v>
       </x:c>
       <x:c r="F24" s="12" t="s">
-        <x:v>72</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="G24" s="12" t="s">
-        <x:v>73</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="H24" s="3"/>
       <x:c r="I24" s="3"/>
@@ -1353,10 +1353,10 @@
     </x:row>
     <x:row r="25" spans="1:11" ht="30" customHeight="1">
       <x:c r="A25" s="13" t="s">
-        <x:v>74</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="B25" s="13" t="s">
-        <x:v>75</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="C25" s="13" t="s">
         <x:v>76</x:v>

--- a/data/positions/Posição Consolidada - 7983962.xlsx
+++ b/data/positions/Posição Consolidada - 7983962.xlsx
@@ -19,7 +19,7 @@
     <x:t>XP</x:t>
   </x:si>
   <x:si>
-    <x:t>Conta: 7983962 | 30/09/2026, 08:51</x:t>
+    <x:t>Conta: 7983962 | 13/10/2026, 11:09</x:t>
   </x:si>
   <x:si>
     <x:t>Este é o seu patrimônio</x:t>
@@ -34,13 +34,13 @@
     <x:t>Saldo projetado</x:t>
   </x:si>
   <x:si>
-    <x:t>20,8%|Renda Fixa</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 2.239.562,47</x:t>
-  </x:si>
-  <x:si>
-    <x:t>20,70%|Pós-Fixada</x:t>
+    <x:t>20,7%|Renda Fixa</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 2.247.311,79</x:t>
+  </x:si>
+  <x:si>
+    <x:t>20,60%|Pós-Fixada</x:t>
   </x:si>
   <x:si>
     <x:t>Aplicação</x:t>
@@ -94,7 +94,7 @@
     <x:t>R$ 1.000.949,68</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 1.043.388,55</x:t>
+    <x:t>R$ 1.046.976,17</x:t>
   </x:si>
   <x:si>
     <x:t>LCI CEF - MAI/2027</x:t>
@@ -118,19 +118,19 @@
     <x:t>R$ 1.191.509,24</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 1.196.173,92</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 1.193.561,70</x:t>
-  </x:si>
-  <x:si>
-    <x:t>24,9%|Operações Compromissadas</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 2.682.256,81</x:t>
-  </x:si>
-  <x:si>
-    <x:t>24,80%|Pós-Fixada</x:t>
+    <x:t>R$ 1.200.335,63</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 1.199.188,20</x:t>
+  </x:si>
+  <x:si>
+    <x:t>25,2%|Operações Compromissadas</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 2.733.803,04</x:t>
+  </x:si>
+  <x:si>
+    <x:t>25,10%|Pós-Fixada</x:t>
   </x:si>
   <x:si>
     <x:t>23/09/2026</x:t>
@@ -142,22 +142,43 @@
     <x:t>85,00% CDI</x:t>
   </x:si>
   <x:si>
-    <x:t>1.683.317,00</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 2.676.474,67</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 2.680.955,83</x:t>
-  </x:si>
-  <x:si>
-    <x:t>54,3%|Fundos de Investimento</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 5.854.883,81</x:t>
-  </x:si>
-  <x:si>
-    <x:t>54,30%|Fundos de Renda Fixa Pós-Fixado</x:t>
+    <x:t>771.230,00</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 1.226.255,99</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 1.233.155,69</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 1.231.603,26</x:t>
+  </x:si>
+  <x:si>
+    <x:t>09/10/2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>12/11/2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>961.538,00</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 1.499.999,99</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 1.500.647,36</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 1.500.501,70</x:t>
+  </x:si>
+  <x:si>
+    <x:t>54,1%|Fundos de Investimento</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 5.880.260,90</x:t>
+  </x:si>
+  <x:si>
+    <x:t>54,10%|Fundos de Renda Fixa Pós-Fixado</x:t>
   </x:si>
   <x:si>
     <x:t>Data cota</x:t>
@@ -175,10 +196,10 @@
     <x:t>XP Bancos FIRF Referenciada DI CP RL</x:t>
   </x:si>
   <x:si>
-    <x:t>29/09/2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 1,95</x:t>
+    <x:t>13/10/2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 1,96</x:t>
   </x:si>
   <x:si>
     <x:t>772.979,35</x:t>
@@ -187,76 +208,73 @@
     <x:t>R$ 0,00</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 1.508.572,08</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 1.503.321,68</x:t>
+    <x:t>R$ 1.515.494,94</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 1.511.648,33</x:t>
   </x:si>
   <x:si>
     <x:t>XP Bancos FIC de FIRF Referenciado DI CP - RL</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 1,54</x:t>
+    <x:t>R$ 1,55</x:t>
   </x:si>
   <x:si>
     <x:t>526.379,08</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 811.285,57</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 809.018,53</x:t>
+    <x:t>R$ 814.934,98</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 812.675,92</x:t>
   </x:si>
   <x:si>
     <x:t>Bradesco SKY FIC FIRF Referenciada DI RL</x:t>
   </x:si>
   <x:si>
-    <x:t>30/09/2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 1.459,43</x:t>
+    <x:t>R$ 1.465,36</x:t>
   </x:si>
   <x:si>
     <x:t>1.188,48</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 1.734.500,59</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 1.728.907,73</x:t>
+    <x:t>R$ 1.741.539,59</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 1.736.764,84</x:t>
   </x:si>
   <x:si>
     <x:t>Bradesco Bancos II FIF CIC RF CP RL</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 1,49</x:t>
+    <x:t>R$ 1,50</x:t>
   </x:si>
   <x:si>
     <x:t>353.356,60</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 527.018,58</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 521.135,10</x:t>
+    <x:t>R$ 529.207,20</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 522.831,28</x:t>
   </x:si>
   <x:si>
     <x:t>Safra Extra Bancos Special FIC FIRF CP</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 143,11</x:t>
+    <x:t>R$ 143,74</x:t>
   </x:si>
   <x:si>
     <x:t>8.898,52</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 1.273.506,99</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 1.263.312,44</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 4,04</x:t>
+    <x:t>R$ 1.279.084,19</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 1.267.634,77</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 186,05</x:t>
   </x:si>
   <x:si>
     <x:t>Resgate de fundo pendente</x:t>
@@ -286,7 +304,7 @@
     <x:t>Saldo Projetado  (D &gt; 3)</x:t>
   </x:si>
   <x:si>
-    <x:t>4,04</x:t>
+    <x:t>186,05</x:t>
   </x:si>
   <x:si>
     <x:t>0</x:t>
@@ -834,7 +852,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:K30"/>
+  <x:dimension ref="A1:K31"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="38.282054" style="0" customWidth="1"/>
@@ -894,13 +912,13 @@
     </x:row>
     <x:row r="4" spans="1:11" ht="30" customHeight="1">
       <x:c r="A4" s="6">
-        <x:v>10776707.1304028</x:v>
+        <x:v>10861561.7878255</x:v>
       </x:c>
       <x:c r="B4" s="7">
-        <x:v>10776703.0904028</x:v>
+        <x:v>10861375.7378255</x:v>
       </x:c>
       <x:c r="C4" s="7">
-        <x:v>4.04</x:v>
+        <x:v>186.05</x:v>
       </x:c>
       <x:c r="D4" s="7">
         <x:v>0</x:v>
@@ -1145,125 +1163,127 @@
       <x:c r="K15" s="3"/>
     </x:row>
     <x:row r="16" spans="1:11" ht="30" customHeight="1">
-      <x:c r="A16" s="13"/>
-      <x:c r="B16" s="13" t="s">
+      <x:c r="A16" s="12"/>
+      <x:c r="B16" s="12" t="s">
         <x:v>39</x:v>
       </x:c>
-      <x:c r="C16" s="13"/>
-      <x:c r="D16" s="13" t="s">
+      <x:c r="C16" s="12"/>
+      <x:c r="D16" s="12" t="s">
         <x:v>40</x:v>
       </x:c>
-      <x:c r="E16" s="13" t="s">
+      <x:c r="E16" s="12" t="s">
         <x:v>41</x:v>
       </x:c>
-      <x:c r="F16" s="13" t="s">
+      <x:c r="F16" s="12" t="s">
         <x:v>42</x:v>
       </x:c>
-      <x:c r="G16" s="13" t="s">
+      <x:c r="G16" s="12" t="s">
         <x:v>24</x:v>
       </x:c>
-      <x:c r="H16" s="13" t="s">
+      <x:c r="H16" s="12" t="s">
         <x:v>43</x:v>
       </x:c>
-      <x:c r="I16" s="13" t="s">
-        <x:v>37</x:v>
-      </x:c>
-      <x:c r="J16" s="13" t="s">
+      <x:c r="I16" s="12" t="s">
         <x:v>44</x:v>
       </x:c>
+      <x:c r="J16" s="12" t="s">
+        <x:v>45</x:v>
+      </x:c>
       <x:c r="K16" s="3"/>
     </x:row>
-    <x:row r="17" spans="1:11">
-      <x:c r="A17" s="4"/>
-      <x:c r="B17" s="4"/>
-      <x:c r="C17" s="4"/>
-      <x:c r="D17" s="4"/>
-      <x:c r="E17" s="4"/>
-      <x:c r="F17" s="4"/>
-      <x:c r="G17" s="4"/>
-      <x:c r="H17" s="4"/>
-      <x:c r="I17" s="4"/>
-      <x:c r="J17" s="4"/>
-      <x:c r="K17" s="4"/>
-    </x:row>
-    <x:row r="18" spans="1:11" ht="45" customHeight="1">
-      <x:c r="A18" s="8" t="s">
-        <x:v>45</x:v>
-      </x:c>
-      <x:c r="B18" s="9"/>
-      <x:c r="C18" s="9"/>
-      <x:c r="D18" s="9"/>
-      <x:c r="E18" s="9"/>
-      <x:c r="F18" s="9"/>
-      <x:c r="G18" s="10" t="s">
+    <x:row r="17" spans="1:11" ht="30" customHeight="1">
+      <x:c r="A17" s="13"/>
+      <x:c r="B17" s="13" t="s">
         <x:v>46</x:v>
       </x:c>
-      <x:c r="H18" s="3"/>
-      <x:c r="I18" s="3"/>
-      <x:c r="J18" s="3"/>
-      <x:c r="K18" s="3"/>
-    </x:row>
-    <x:row r="19" spans="1:11">
-      <x:c r="A19" s="4"/>
-      <x:c r="B19" s="4"/>
-      <x:c r="C19" s="4"/>
-      <x:c r="D19" s="4"/>
-      <x:c r="E19" s="4"/>
-      <x:c r="F19" s="4"/>
-      <x:c r="G19" s="4"/>
+      <x:c r="C17" s="13"/>
+      <x:c r="D17" s="13" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="E17" s="13" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="F17" s="13" t="s">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="G17" s="13" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="H17" s="13" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="I17" s="13" t="s">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="J17" s="13" t="s">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="K17" s="3"/>
+    </x:row>
+    <x:row r="18" spans="1:11">
+      <x:c r="A18" s="4"/>
+      <x:c r="B18" s="4"/>
+      <x:c r="C18" s="4"/>
+      <x:c r="D18" s="4"/>
+      <x:c r="E18" s="4"/>
+      <x:c r="F18" s="4"/>
+      <x:c r="G18" s="4"/>
+      <x:c r="H18" s="4"/>
+      <x:c r="I18" s="4"/>
+      <x:c r="J18" s="4"/>
+      <x:c r="K18" s="4"/>
+    </x:row>
+    <x:row r="19" spans="1:11" ht="45" customHeight="1">
+      <x:c r="A19" s="8" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="B19" s="9"/>
+      <x:c r="C19" s="9"/>
+      <x:c r="D19" s="9"/>
+      <x:c r="E19" s="9"/>
+      <x:c r="F19" s="9"/>
+      <x:c r="G19" s="10" t="s">
+        <x:v>53</x:v>
+      </x:c>
       <x:c r="H19" s="3"/>
       <x:c r="I19" s="3"/>
       <x:c r="J19" s="3"/>
       <x:c r="K19" s="3"/>
     </x:row>
-    <x:row r="20" spans="1:11" ht="35.1" customHeight="1">
-      <x:c r="A20" s="11" t="s">
-        <x:v>47</x:v>
-      </x:c>
-      <x:c r="B20" s="11" t="s">
-        <x:v>48</x:v>
-      </x:c>
-      <x:c r="C20" s="11" t="s">
-        <x:v>49</x:v>
-      </x:c>
-      <x:c r="D20" s="11" t="s">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="E20" s="11" t="s">
-        <x:v>51</x:v>
-      </x:c>
-      <x:c r="F20" s="11" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="G20" s="11" t="s">
-        <x:v>17</x:v>
-      </x:c>
+    <x:row r="20" spans="1:11">
+      <x:c r="A20" s="4"/>
+      <x:c r="B20" s="4"/>
+      <x:c r="C20" s="4"/>
+      <x:c r="D20" s="4"/>
+      <x:c r="E20" s="4"/>
+      <x:c r="F20" s="4"/>
+      <x:c r="G20" s="4"/>
       <x:c r="H20" s="3"/>
       <x:c r="I20" s="3"/>
       <x:c r="J20" s="3"/>
       <x:c r="K20" s="3"/>
     </x:row>
-    <x:row r="21" spans="1:11" ht="30" customHeight="1">
-      <x:c r="A21" s="12" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="B21" s="12" t="s">
-        <x:v>53</x:v>
-      </x:c>
-      <x:c r="C21" s="12" t="s">
+    <x:row r="21" spans="1:11" ht="35.1" customHeight="1">
+      <x:c r="A21" s="11" t="s">
         <x:v>54</x:v>
       </x:c>
-      <x:c r="D21" s="12" t="s">
+      <x:c r="B21" s="11" t="s">
         <x:v>55</x:v>
       </x:c>
-      <x:c r="E21" s="12" t="s">
+      <x:c r="C21" s="11" t="s">
         <x:v>56</x:v>
       </x:c>
-      <x:c r="F21" s="12" t="s">
+      <x:c r="D21" s="11" t="s">
         <x:v>57</x:v>
       </x:c>
-      <x:c r="G21" s="12" t="s">
+      <x:c r="E21" s="11" t="s">
         <x:v>58</x:v>
+      </x:c>
+      <x:c r="F21" s="11" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="G21" s="11" t="s">
+        <x:v>17</x:v>
       </x:c>
       <x:c r="H21" s="3"/>
       <x:c r="I21" s="3"/>
@@ -1275,22 +1295,22 @@
         <x:v>59</x:v>
       </x:c>
       <x:c r="B22" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="C22" s="12" t="s">
-        <x:v>60</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="D22" s="12" t="s">
-        <x:v>61</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="E22" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="F22" s="12" t="s">
-        <x:v>62</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="G22" s="12" t="s">
-        <x:v>63</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="H22" s="3"/>
       <x:c r="I22" s="3"/>
@@ -1299,25 +1319,25 @@
     </x:row>
     <x:row r="23" spans="1:11" ht="30" customHeight="1">
       <x:c r="A23" s="12" t="s">
-        <x:v>64</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="B23" s="12" t="s">
-        <x:v>65</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="C23" s="12" t="s">
-        <x:v>66</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="D23" s="12" t="s">
-        <x:v>67</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="E23" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="F23" s="12" t="s">
-        <x:v>68</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="G23" s="12" t="s">
-        <x:v>69</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="H23" s="3"/>
       <x:c r="I23" s="3"/>
@@ -1326,25 +1346,25 @@
     </x:row>
     <x:row r="24" spans="1:11" ht="30" customHeight="1">
       <x:c r="A24" s="12" t="s">
-        <x:v>70</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="B24" s="12" t="s">
-        <x:v>65</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="C24" s="12" t="s">
-        <x:v>71</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="D24" s="12" t="s">
-        <x:v>72</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="E24" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="F24" s="12" t="s">
-        <x:v>73</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="G24" s="12" t="s">
-        <x:v>74</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="H24" s="3"/>
       <x:c r="I24" s="3"/>
@@ -1352,143 +1372,170 @@
       <x:c r="K24" s="3"/>
     </x:row>
     <x:row r="25" spans="1:11" ht="30" customHeight="1">
-      <x:c r="A25" s="13" t="s">
-        <x:v>75</x:v>
-      </x:c>
-      <x:c r="B25" s="13" t="s">
-        <x:v>53</x:v>
-      </x:c>
-      <x:c r="C25" s="13" t="s">
+      <x:c r="A25" s="12" t="s">
         <x:v>76</x:v>
       </x:c>
-      <x:c r="D25" s="13" t="s">
+      <x:c r="B25" s="12" t="s">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="C25" s="12" t="s">
         <x:v>77</x:v>
       </x:c>
-      <x:c r="E25" s="13" t="s">
-        <x:v>56</x:v>
-      </x:c>
-      <x:c r="F25" s="13" t="s">
+      <x:c r="D25" s="12" t="s">
         <x:v>78</x:v>
       </x:c>
-      <x:c r="G25" s="13" t="s">
+      <x:c r="E25" s="12" t="s">
+        <x:v>63</x:v>
+      </x:c>
+      <x:c r="F25" s="12" t="s">
         <x:v>79</x:v>
+      </x:c>
+      <x:c r="G25" s="12" t="s">
+        <x:v>80</x:v>
       </x:c>
       <x:c r="H25" s="3"/>
       <x:c r="I25" s="3"/>
       <x:c r="J25" s="3"/>
       <x:c r="K25" s="3"/>
     </x:row>
-    <x:row r="26" spans="1:11">
-      <x:c r="A26" s="4"/>
-      <x:c r="B26" s="4"/>
-      <x:c r="C26" s="4"/>
-      <x:c r="D26" s="4"/>
-      <x:c r="E26" s="4"/>
-      <x:c r="F26" s="4"/>
-      <x:c r="G26" s="4"/>
-      <x:c r="H26" s="4"/>
-      <x:c r="I26" s="4"/>
-      <x:c r="J26" s="4"/>
-      <x:c r="K26" s="4"/>
-    </x:row>
-    <x:row r="27" spans="1:11" ht="45" customHeight="1">
-      <x:c r="A27" s="8" t="s">
+    <x:row r="26" spans="1:11" ht="30" customHeight="1">
+      <x:c r="A26" s="13" t="s">
+        <x:v>81</x:v>
+      </x:c>
+      <x:c r="B26" s="13" t="s">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="C26" s="13" t="s">
+        <x:v>82</x:v>
+      </x:c>
+      <x:c r="D26" s="13" t="s">
+        <x:v>83</x:v>
+      </x:c>
+      <x:c r="E26" s="13" t="s">
+        <x:v>63</x:v>
+      </x:c>
+      <x:c r="F26" s="13" t="s">
+        <x:v>84</x:v>
+      </x:c>
+      <x:c r="G26" s="13" t="s">
+        <x:v>85</x:v>
+      </x:c>
+      <x:c r="H26" s="3"/>
+      <x:c r="I26" s="3"/>
+      <x:c r="J26" s="3"/>
+      <x:c r="K26" s="3"/>
+    </x:row>
+    <x:row r="27" spans="1:11">
+      <x:c r="A27" s="4"/>
+      <x:c r="B27" s="4"/>
+      <x:c r="C27" s="4"/>
+      <x:c r="D27" s="4"/>
+      <x:c r="E27" s="4"/>
+      <x:c r="F27" s="4"/>
+      <x:c r="G27" s="4"/>
+      <x:c r="H27" s="4"/>
+      <x:c r="I27" s="4"/>
+      <x:c r="J27" s="4"/>
+      <x:c r="K27" s="4"/>
+    </x:row>
+    <x:row r="28" spans="1:11" ht="45" customHeight="1">
+      <x:c r="A28" s="8" t="s">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="B27" s="9"/>
-      <x:c r="C27" s="9"/>
-      <x:c r="D27" s="9"/>
-      <x:c r="E27" s="9"/>
-      <x:c r="F27" s="9"/>
-      <x:c r="G27" s="9"/>
-      <x:c r="H27" s="9"/>
-      <x:c r="I27" s="9"/>
-      <x:c r="J27" s="9"/>
-      <x:c r="K27" s="10" t="s">
-        <x:v>80</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="28" spans="1:11">
-      <x:c r="A28" s="4"/>
-      <x:c r="B28" s="4"/>
-      <x:c r="C28" s="4"/>
-      <x:c r="D28" s="4"/>
-      <x:c r="E28" s="4"/>
-      <x:c r="F28" s="4"/>
-      <x:c r="G28" s="4"/>
-      <x:c r="H28" s="4"/>
-      <x:c r="I28" s="4"/>
-      <x:c r="J28" s="4"/>
-      <x:c r="K28" s="4"/>
-    </x:row>
-    <x:row r="29" spans="1:11" ht="35.1" customHeight="1">
-      <x:c r="A29" s="11" t="s">
+      <x:c r="B28" s="9"/>
+      <x:c r="C28" s="9"/>
+      <x:c r="D28" s="9"/>
+      <x:c r="E28" s="9"/>
+      <x:c r="F28" s="9"/>
+      <x:c r="G28" s="9"/>
+      <x:c r="H28" s="9"/>
+      <x:c r="I28" s="9"/>
+      <x:c r="J28" s="9"/>
+      <x:c r="K28" s="10" t="s">
+        <x:v>86</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="29" spans="1:11">
+      <x:c r="A29" s="4"/>
+      <x:c r="B29" s="4"/>
+      <x:c r="C29" s="4"/>
+      <x:c r="D29" s="4"/>
+      <x:c r="E29" s="4"/>
+      <x:c r="F29" s="4"/>
+      <x:c r="G29" s="4"/>
+      <x:c r="H29" s="4"/>
+      <x:c r="I29" s="4"/>
+      <x:c r="J29" s="4"/>
+      <x:c r="K29" s="4"/>
+    </x:row>
+    <x:row r="30" spans="1:11" ht="35.1" customHeight="1">
+      <x:c r="A30" s="11" t="s">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="B29" s="11" t="s">
+      <x:c r="B30" s="11" t="s">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="C29" s="11" t="s">
-        <x:v>81</x:v>
-      </x:c>
-      <x:c r="D29" s="11" t="s">
-        <x:v>82</x:v>
-      </x:c>
-      <x:c r="E29" s="11" t="s">
-        <x:v>83</x:v>
-      </x:c>
-      <x:c r="F29" s="11" t="s">
-        <x:v>84</x:v>
-      </x:c>
-      <x:c r="G29" s="11" t="s">
-        <x:v>85</x:v>
-      </x:c>
-      <x:c r="H29" s="11" t="s">
-        <x:v>86</x:v>
-      </x:c>
-      <x:c r="I29" s="11" t="s">
+      <x:c r="C30" s="11" t="s">
         <x:v>87</x:v>
       </x:c>
-      <x:c r="J29" s="11" t="s">
+      <x:c r="D30" s="11" t="s">
         <x:v>88</x:v>
       </x:c>
-      <x:c r="K29" s="11" t="s">
+      <x:c r="E30" s="11" t="s">
         <x:v>89</x:v>
       </x:c>
-    </x:row>
-    <x:row r="30" spans="1:11" ht="30" customHeight="1">
-      <x:c r="A30" s="13" t="s">
+      <x:c r="F30" s="11" t="s">
         <x:v>90</x:v>
       </x:c>
-      <x:c r="B30" s="13" t="s">
+      <x:c r="G30" s="11" t="s">
         <x:v>91</x:v>
       </x:c>
-      <x:c r="C30" s="13" t="s">
-        <x:v>91</x:v>
-      </x:c>
-      <x:c r="D30" s="13" t="s">
-        <x:v>91</x:v>
-      </x:c>
-      <x:c r="E30" s="13" t="s">
-        <x:v>91</x:v>
-      </x:c>
-      <x:c r="F30" s="13" t="s">
-        <x:v>91</x:v>
-      </x:c>
-      <x:c r="G30" s="13" t="s">
-        <x:v>91</x:v>
-      </x:c>
-      <x:c r="H30" s="13" t="s">
-        <x:v>91</x:v>
-      </x:c>
-      <x:c r="I30" s="13" t="s">
-        <x:v>91</x:v>
-      </x:c>
-      <x:c r="J30" s="13" t="s">
-        <x:v>91</x:v>
-      </x:c>
-      <x:c r="K30" s="13" t="s">
-        <x:v>91</x:v>
+      <x:c r="H30" s="11" t="s">
+        <x:v>92</x:v>
+      </x:c>
+      <x:c r="I30" s="11" t="s">
+        <x:v>93</x:v>
+      </x:c>
+      <x:c r="J30" s="11" t="s">
+        <x:v>94</x:v>
+      </x:c>
+      <x:c r="K30" s="11" t="s">
+        <x:v>95</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="31" spans="1:11" ht="30" customHeight="1">
+      <x:c r="A31" s="13" t="s">
+        <x:v>96</x:v>
+      </x:c>
+      <x:c r="B31" s="13" t="s">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="C31" s="13" t="s">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="D31" s="13" t="s">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="E31" s="13" t="s">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="F31" s="13" t="s">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="G31" s="13" t="s">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="H31" s="13" t="s">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="I31" s="13" t="s">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="J31" s="13" t="s">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="K31" s="13" t="s">
+        <x:v>97</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -1497,8 +1544,8 @@
     <x:mergeCell ref="F1:G1"/>
     <x:mergeCell ref="A7:F7"/>
     <x:mergeCell ref="A13:F13"/>
-    <x:mergeCell ref="A18:F18"/>
-    <x:mergeCell ref="A27:J27"/>
+    <x:mergeCell ref="A19:F19"/>
+    <x:mergeCell ref="A28:J28"/>
   </x:mergeCells>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>

--- a/data/positions/Posição Consolidada - 7983962.xlsx
+++ b/data/positions/Posição Consolidada - 7983962.xlsx
@@ -19,7 +19,7 @@
     <x:t>XP</x:t>
   </x:si>
   <x:si>
-    <x:t>Conta: 7983962 | 13/10/2026, 11:09</x:t>
+    <x:t>Conta: 7983962 | 14/10/2026, 08:48</x:t>
   </x:si>
   <x:si>
     <x:t>Este é o seu patrimônio</x:t>
@@ -37,7 +37,7 @@
     <x:t>20,7%|Renda Fixa</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 2.247.311,79</x:t>
+    <x:t>R$ 2.248.282,34</x:t>
   </x:si>
   <x:si>
     <x:t>20,60%|Pós-Fixada</x:t>
@@ -94,7 +94,7 @@
     <x:t>R$ 1.000.949,68</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 1.046.976,17</x:t>
+    <x:t>R$ 1.047.425,49</x:t>
   </x:si>
   <x:si>
     <x:t>LCI CEF - MAI/2027</x:t>
@@ -118,16 +118,16 @@
     <x:t>R$ 1.191.509,24</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 1.200.335,63</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 1.199.188,20</x:t>
+    <x:t>R$ 1.200.856,86</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 1.199.922,10</x:t>
   </x:si>
   <x:si>
     <x:t>25,2%|Operações Compromissadas</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 2.733.803,04</x:t>
+    <x:t>R$ 2.734.983,47</x:t>
   </x:si>
   <x:si>
     <x:t>25,10%|Pós-Fixada</x:t>
@@ -148,10 +148,10 @@
     <x:t>R$ 1.226.255,99</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 1.233.155,69</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 1.231.603,26</x:t>
+    <x:t>R$ 1.233.688,04</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 1.232.015,83</x:t>
   </x:si>
   <x:si>
     <x:t>09/10/2026</x:t>
@@ -166,10 +166,10 @@
     <x:t>R$ 1.499.999,99</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 1.500.647,36</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 1.500.501,70</x:t>
+    <x:t>R$ 1.501.295,43</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 1.501.003,96</x:t>
   </x:si>
   <x:si>
     <x:t>54,1%|Fundos de Investimento</x:t>
@@ -274,7 +274,10 @@
     <x:t>R$ 1.267.634,77</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 186,05</x:t>
+    <x:t>0,01%|Saldo projetado</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 1.613,85</x:t>
   </x:si>
   <x:si>
     <x:t>Resgate de fundo pendente</x:t>
@@ -308,6 +311,9 @@
   </x:si>
   <x:si>
     <x:t>0</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1427,8</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -912,16 +918,16 @@
     </x:row>
     <x:row r="4" spans="1:11" ht="30" customHeight="1">
       <x:c r="A4" s="6">
-        <x:v>10861561.7878255</x:v>
+        <x:v>10865140.5631086</x:v>
       </x:c>
       <x:c r="B4" s="7">
-        <x:v>10861375.7378255</x:v>
+        <x:v>10863526.7131086</x:v>
       </x:c>
       <x:c r="C4" s="7">
         <x:v>186.05</x:v>
       </x:c>
       <x:c r="D4" s="7">
-        <x:v>0</x:v>
+        <x:v>1427.8</x:v>
       </x:c>
       <x:c r="E4" s="4"/>
       <x:c r="F4" s="4"/>
@@ -1440,7 +1446,7 @@
     </x:row>
     <x:row r="28" spans="1:11" ht="45" customHeight="1">
       <x:c r="A28" s="8" t="s">
-        <x:v>5</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="B28" s="9"/>
       <x:c r="C28" s="9"/>
@@ -1452,7 +1458,7 @@
       <x:c r="I28" s="9"/>
       <x:c r="J28" s="9"/>
       <x:c r="K28" s="10" t="s">
-        <x:v>86</x:v>
+        <x:v>87</x:v>
       </x:c>
     </x:row>
     <x:row r="29" spans="1:11">
@@ -1476,66 +1482,66 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="C30" s="11" t="s">
-        <x:v>87</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="D30" s="11" t="s">
-        <x:v>88</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="E30" s="11" t="s">
-        <x:v>89</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="F30" s="11" t="s">
-        <x:v>90</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="G30" s="11" t="s">
-        <x:v>91</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="H30" s="11" t="s">
-        <x:v>92</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="I30" s="11" t="s">
-        <x:v>93</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="J30" s="11" t="s">
-        <x:v>94</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="K30" s="11" t="s">
-        <x:v>95</x:v>
+        <x:v>96</x:v>
       </x:c>
     </x:row>
     <x:row r="31" spans="1:11" ht="30" customHeight="1">
       <x:c r="A31" s="13" t="s">
-        <x:v>96</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="B31" s="13" t="s">
-        <x:v>97</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="C31" s="13" t="s">
-        <x:v>97</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="D31" s="13" t="s">
-        <x:v>97</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="E31" s="13" t="s">
-        <x:v>97</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="F31" s="13" t="s">
-        <x:v>97</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="G31" s="13" t="s">
-        <x:v>97</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="H31" s="13" t="s">
-        <x:v>97</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="I31" s="13" t="s">
-        <x:v>97</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="J31" s="13" t="s">
-        <x:v>97</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="K31" s="13" t="s">
-        <x:v>97</x:v>
+        <x:v>98</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/data/positions/Posição Consolidada - 7983962.xlsx
+++ b/data/positions/Posição Consolidada - 7983962.xlsx
@@ -19,7 +19,7 @@
     <x:t>XP</x:t>
   </x:si>
   <x:si>
-    <x:t>Conta: 7983962 | 14/10/2026, 08:48</x:t>
+    <x:t>Conta: 7983962 | 27/10/2026, 19:00</x:t>
   </x:si>
   <x:si>
     <x:t>Este é o seu patrimônio</x:t>
@@ -37,7 +37,7 @@
     <x:t>20,7%|Renda Fixa</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 2.248.282,34</x:t>
+    <x:t>R$ 2.257.036,17</x:t>
   </x:si>
   <x:si>
     <x:t>20,60%|Pós-Fixada</x:t>
@@ -94,7 +94,7 @@
     <x:t>R$ 1.000.949,68</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 1.047.425,49</x:t>
+    <x:t>R$ 1.051.478,04</x:t>
   </x:si>
   <x:si>
     <x:t>LCI CEF - MAI/2027</x:t>
@@ -118,64 +118,55 @@
     <x:t>R$ 1.191.509,24</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 1.200.856,86</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 1.199.922,10</x:t>
+    <x:t>R$ 1.205.558,13</x:t>
   </x:si>
   <x:si>
     <x:t>25,2%|Operações Compromissadas</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 2.734.983,47</x:t>
+    <x:t>R$ 2.744.137,74</x:t>
   </x:si>
   <x:si>
     <x:t>25,10%|Pós-Fixada</x:t>
   </x:si>
   <x:si>
-    <x:t>23/09/2026</x:t>
+    <x:t>09/10/2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>12/11/2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>85,00% CDI</x:t>
+  </x:si>
+  <x:si>
+    <x:t>961.538,00</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 1.499.999,99</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 1.507.137,74</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 1.505.531,75</x:t>
   </x:si>
   <x:si>
     <x:t>27/10/2026</x:t>
   </x:si>
   <x:si>
-    <x:t>85,00% CDI</x:t>
-  </x:si>
-  <x:si>
-    <x:t>771.230,00</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 1.226.255,99</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 1.233.688,04</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 1.232.015,83</x:t>
-  </x:si>
-  <x:si>
-    <x:t>09/10/2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>12/11/2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>961.538,00</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 1.499.999,99</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 1.501.295,43</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 1.501.003,96</x:t>
-  </x:si>
-  <x:si>
-    <x:t>54,1%|Fundos de Investimento</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 5.880.260,90</x:t>
+    <x:t>30/11/2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>935,00</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 1.237.000,00</x:t>
+  </x:si>
+  <x:si>
+    <x:t>54,2%|Fundos de Investimento</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 5.909.245,53</x:t>
   </x:si>
   <x:si>
     <x:t>54,10%|Fundos de Renda Fixa Pós-Fixado</x:t>
@@ -196,10 +187,7 @@
     <x:t>XP Bancos FIRF Referenciada DI CP RL</x:t>
   </x:si>
   <x:si>
-    <x:t>13/10/2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 1,96</x:t>
+    <x:t>R$ 1,97</x:t>
   </x:si>
   <x:si>
     <x:t>772.979,35</x:t>
@@ -208,76 +196,73 @@
     <x:t>R$ 0,00</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 1.515.494,94</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 1.511.648,33</x:t>
+    <x:t>R$ 1.523.330,26</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 1.518.080,95</x:t>
   </x:si>
   <x:si>
     <x:t>XP Bancos FIC de FIRF Referenciado DI CP - RL</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 1,55</x:t>
+    <x:t>R$ 1,56</x:t>
   </x:si>
   <x:si>
     <x:t>526.379,08</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 814.934,98</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 812.675,92</x:t>
+    <x:t>R$ 819.062,82</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 816.573,69</x:t>
   </x:si>
   <x:si>
     <x:t>Bradesco SKY FIC FIRF Referenciada DI RL</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 1.465,36</x:t>
+    <x:t>R$ 1.472,21</x:t>
   </x:si>
   <x:si>
     <x:t>1.188,48</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 1.741.539,59</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 1.736.764,84</x:t>
+    <x:t>R$ 1.749.679,25</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 1.743.307,88</x:t>
   </x:si>
   <x:si>
     <x:t>Bradesco Bancos II FIF CIC RF CP RL</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 1,50</x:t>
+    <x:t>R$ 1,51</x:t>
   </x:si>
   <x:si>
     <x:t>353.356,60</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 529.207,20</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 522.831,28</x:t>
+    <x:t>R$ 531.914,65</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 524.929,56</x:t>
   </x:si>
   <x:si>
     <x:t>Safra Extra Bancos Special FIC FIRF CP</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 143,74</x:t>
+    <x:t>R$ 144,44</x:t>
   </x:si>
   <x:si>
     <x:t>8.898,52</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 1.279.084,19</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 1.267.634,77</x:t>
-  </x:si>
-  <x:si>
-    <x:t>0,01%|Saldo projetado</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 1.613,85</x:t>
+    <x:t>R$ 1.285.258,55</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 1.272.419,89</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 350,85</x:t>
   </x:si>
   <x:si>
     <x:t>Resgate de fundo pendente</x:t>
@@ -307,13 +292,10 @@
     <x:t>Saldo Projetado  (D &gt; 3)</x:t>
   </x:si>
   <x:si>
-    <x:t>186,05</x:t>
+    <x:t>350,85</x:t>
   </x:si>
   <x:si>
     <x:t>0</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1427,8</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -918,16 +900,16 @@
     </x:row>
     <x:row r="4" spans="1:11" ht="30" customHeight="1">
       <x:c r="A4" s="6">
-        <x:v>10865140.5631086</x:v>
+        <x:v>10910770.2914802</x:v>
       </x:c>
       <x:c r="B4" s="7">
-        <x:v>10863526.7131086</x:v>
+        <x:v>10910419.4414802</x:v>
       </x:c>
       <x:c r="C4" s="7">
-        <x:v>186.05</x:v>
+        <x:v>350.85</x:v>
       </x:c>
       <x:c r="D4" s="7">
-        <x:v>1427.8</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E4" s="4"/>
       <x:c r="F4" s="4"/>
@@ -1088,7 +1070,7 @@
         <x:v>34</x:v>
       </x:c>
       <x:c r="J11" s="13" t="s">
-        <x:v>35</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="K11" s="3"/>
     </x:row>
@@ -1107,7 +1089,7 @@
     </x:row>
     <x:row r="13" spans="1:11" ht="45" customHeight="1">
       <x:c r="A13" s="8" t="s">
-        <x:v>36</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="B13" s="9"/>
       <x:c r="C13" s="9"/>
@@ -1115,7 +1097,7 @@
       <x:c r="E13" s="9"/>
       <x:c r="F13" s="9"/>
       <x:c r="G13" s="10" t="s">
-        <x:v>37</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="H13" s="3"/>
       <x:c r="I13" s="3"/>
@@ -1137,7 +1119,7 @@
     </x:row>
     <x:row r="15" spans="1:11" ht="35.1" customHeight="1">
       <x:c r="A15" s="11" t="s">
-        <x:v>38</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="B15" s="11" t="s">
         <x:v>9</x:v>
@@ -1171,58 +1153,58 @@
     <x:row r="16" spans="1:11" ht="30" customHeight="1">
       <x:c r="A16" s="12"/>
       <x:c r="B16" s="12" t="s">
-        <x:v>39</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="C16" s="12"/>
       <x:c r="D16" s="12" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="E16" s="12" t="s">
         <x:v>40</x:v>
       </x:c>
-      <x:c r="E16" s="12" t="s">
+      <x:c r="F16" s="12" t="s">
         <x:v>41</x:v>
-      </x:c>
-      <x:c r="F16" s="12" t="s">
-        <x:v>42</x:v>
       </x:c>
       <x:c r="G16" s="12" t="s">
         <x:v>24</x:v>
       </x:c>
       <x:c r="H16" s="12" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="I16" s="12" t="s">
         <x:v>43</x:v>
       </x:c>
-      <x:c r="I16" s="12" t="s">
+      <x:c r="J16" s="12" t="s">
         <x:v>44</x:v>
-      </x:c>
-      <x:c r="J16" s="12" t="s">
-        <x:v>45</x:v>
       </x:c>
       <x:c r="K16" s="3"/>
     </x:row>
     <x:row r="17" spans="1:11" ht="30" customHeight="1">
       <x:c r="A17" s="13"/>
       <x:c r="B17" s="13" t="s">
-        <x:v>46</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="C17" s="13"/>
       <x:c r="D17" s="13" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="E17" s="13" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="F17" s="13" t="s">
         <x:v>47</x:v>
-      </x:c>
-      <x:c r="E17" s="13" t="s">
-        <x:v>41</x:v>
-      </x:c>
-      <x:c r="F17" s="13" t="s">
-        <x:v>48</x:v>
       </x:c>
       <x:c r="G17" s="13" t="s">
         <x:v>24</x:v>
       </x:c>
       <x:c r="H17" s="13" t="s">
-        <x:v>49</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="I17" s="13" t="s">
-        <x:v>50</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="J17" s="13" t="s">
-        <x:v>51</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="K17" s="3"/>
     </x:row>
@@ -1241,7 +1223,7 @@
     </x:row>
     <x:row r="19" spans="1:11" ht="45" customHeight="1">
       <x:c r="A19" s="8" t="s">
-        <x:v>52</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="B19" s="9"/>
       <x:c r="C19" s="9"/>
@@ -1249,7 +1231,7 @@
       <x:c r="E19" s="9"/>
       <x:c r="F19" s="9"/>
       <x:c r="G19" s="10" t="s">
-        <x:v>53</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="H19" s="3"/>
       <x:c r="I19" s="3"/>
@@ -1271,19 +1253,19 @@
     </x:row>
     <x:row r="21" spans="1:11" ht="35.1" customHeight="1">
       <x:c r="A21" s="11" t="s">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="B21" s="11" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="C21" s="11" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="D21" s="11" t="s">
         <x:v>54</x:v>
       </x:c>
-      <x:c r="B21" s="11" t="s">
+      <x:c r="E21" s="11" t="s">
         <x:v>55</x:v>
-      </x:c>
-      <x:c r="C21" s="11" t="s">
-        <x:v>56</x:v>
-      </x:c>
-      <x:c r="D21" s="11" t="s">
-        <x:v>57</x:v>
-      </x:c>
-      <x:c r="E21" s="11" t="s">
-        <x:v>58</x:v>
       </x:c>
       <x:c r="F21" s="11" t="s">
         <x:v>16</x:v>
@@ -1298,25 +1280,25 @@
     </x:row>
     <x:row r="22" spans="1:11" ht="30" customHeight="1">
       <x:c r="A22" s="12" t="s">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="B22" s="12" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="C22" s="12" t="s">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="D22" s="12" t="s">
+        <x:v>58</x:v>
+      </x:c>
+      <x:c r="E22" s="12" t="s">
         <x:v>59</x:v>
       </x:c>
-      <x:c r="B22" s="12" t="s">
+      <x:c r="F22" s="12" t="s">
         <x:v>60</x:v>
       </x:c>
-      <x:c r="C22" s="12" t="s">
+      <x:c r="G22" s="12" t="s">
         <x:v>61</x:v>
-      </x:c>
-      <x:c r="D22" s="12" t="s">
-        <x:v>62</x:v>
-      </x:c>
-      <x:c r="E22" s="12" t="s">
-        <x:v>63</x:v>
-      </x:c>
-      <x:c r="F22" s="12" t="s">
-        <x:v>64</x:v>
-      </x:c>
-      <x:c r="G22" s="12" t="s">
-        <x:v>65</x:v>
       </x:c>
       <x:c r="H22" s="3"/>
       <x:c r="I22" s="3"/>
@@ -1325,25 +1307,25 @@
     </x:row>
     <x:row r="23" spans="1:11" ht="30" customHeight="1">
       <x:c r="A23" s="12" t="s">
+        <x:v>62</x:v>
+      </x:c>
+      <x:c r="B23" s="12" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="C23" s="12" t="s">
+        <x:v>63</x:v>
+      </x:c>
+      <x:c r="D23" s="12" t="s">
+        <x:v>64</x:v>
+      </x:c>
+      <x:c r="E23" s="12" t="s">
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="F23" s="12" t="s">
+        <x:v>65</x:v>
+      </x:c>
+      <x:c r="G23" s="12" t="s">
         <x:v>66</x:v>
-      </x:c>
-      <x:c r="B23" s="12" t="s">
-        <x:v>60</x:v>
-      </x:c>
-      <x:c r="C23" s="12" t="s">
-        <x:v>67</x:v>
-      </x:c>
-      <x:c r="D23" s="12" t="s">
-        <x:v>68</x:v>
-      </x:c>
-      <x:c r="E23" s="12" t="s">
-        <x:v>63</x:v>
-      </x:c>
-      <x:c r="F23" s="12" t="s">
-        <x:v>69</x:v>
-      </x:c>
-      <x:c r="G23" s="12" t="s">
-        <x:v>70</x:v>
       </x:c>
       <x:c r="H23" s="3"/>
       <x:c r="I23" s="3"/>
@@ -1352,25 +1334,25 @@
     </x:row>
     <x:row r="24" spans="1:11" ht="30" customHeight="1">
       <x:c r="A24" s="12" t="s">
+        <x:v>67</x:v>
+      </x:c>
+      <x:c r="B24" s="12" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="C24" s="12" t="s">
+        <x:v>68</x:v>
+      </x:c>
+      <x:c r="D24" s="12" t="s">
+        <x:v>69</x:v>
+      </x:c>
+      <x:c r="E24" s="12" t="s">
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="F24" s="12" t="s">
+        <x:v>70</x:v>
+      </x:c>
+      <x:c r="G24" s="12" t="s">
         <x:v>71</x:v>
-      </x:c>
-      <x:c r="B24" s="12" t="s">
-        <x:v>60</x:v>
-      </x:c>
-      <x:c r="C24" s="12" t="s">
-        <x:v>72</x:v>
-      </x:c>
-      <x:c r="D24" s="12" t="s">
-        <x:v>73</x:v>
-      </x:c>
-      <x:c r="E24" s="12" t="s">
-        <x:v>63</x:v>
-      </x:c>
-      <x:c r="F24" s="12" t="s">
-        <x:v>74</x:v>
-      </x:c>
-      <x:c r="G24" s="12" t="s">
-        <x:v>75</x:v>
       </x:c>
       <x:c r="H24" s="3"/>
       <x:c r="I24" s="3"/>
@@ -1379,25 +1361,25 @@
     </x:row>
     <x:row r="25" spans="1:11" ht="30" customHeight="1">
       <x:c r="A25" s="12" t="s">
+        <x:v>72</x:v>
+      </x:c>
+      <x:c r="B25" s="12" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="C25" s="12" t="s">
+        <x:v>73</x:v>
+      </x:c>
+      <x:c r="D25" s="12" t="s">
+        <x:v>74</x:v>
+      </x:c>
+      <x:c r="E25" s="12" t="s">
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="F25" s="12" t="s">
+        <x:v>75</x:v>
+      </x:c>
+      <x:c r="G25" s="12" t="s">
         <x:v>76</x:v>
-      </x:c>
-      <x:c r="B25" s="12" t="s">
-        <x:v>60</x:v>
-      </x:c>
-      <x:c r="C25" s="12" t="s">
-        <x:v>77</x:v>
-      </x:c>
-      <x:c r="D25" s="12" t="s">
-        <x:v>78</x:v>
-      </x:c>
-      <x:c r="E25" s="12" t="s">
-        <x:v>63</x:v>
-      </x:c>
-      <x:c r="F25" s="12" t="s">
-        <x:v>79</x:v>
-      </x:c>
-      <x:c r="G25" s="12" t="s">
-        <x:v>80</x:v>
       </x:c>
       <x:c r="H25" s="3"/>
       <x:c r="I25" s="3"/>
@@ -1406,25 +1388,25 @@
     </x:row>
     <x:row r="26" spans="1:11" ht="30" customHeight="1">
       <x:c r="A26" s="13" t="s">
+        <x:v>77</x:v>
+      </x:c>
+      <x:c r="B26" s="13" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="C26" s="13" t="s">
+        <x:v>78</x:v>
+      </x:c>
+      <x:c r="D26" s="13" t="s">
+        <x:v>79</x:v>
+      </x:c>
+      <x:c r="E26" s="13" t="s">
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="F26" s="13" t="s">
+        <x:v>80</x:v>
+      </x:c>
+      <x:c r="G26" s="13" t="s">
         <x:v>81</x:v>
-      </x:c>
-      <x:c r="B26" s="13" t="s">
-        <x:v>60</x:v>
-      </x:c>
-      <x:c r="C26" s="13" t="s">
-        <x:v>82</x:v>
-      </x:c>
-      <x:c r="D26" s="13" t="s">
-        <x:v>83</x:v>
-      </x:c>
-      <x:c r="E26" s="13" t="s">
-        <x:v>63</x:v>
-      </x:c>
-      <x:c r="F26" s="13" t="s">
-        <x:v>84</x:v>
-      </x:c>
-      <x:c r="G26" s="13" t="s">
-        <x:v>85</x:v>
       </x:c>
       <x:c r="H26" s="3"/>
       <x:c r="I26" s="3"/>
@@ -1446,7 +1428,7 @@
     </x:row>
     <x:row r="28" spans="1:11" ht="45" customHeight="1">
       <x:c r="A28" s="8" t="s">
-        <x:v>86</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="B28" s="9"/>
       <x:c r="C28" s="9"/>
@@ -1458,7 +1440,7 @@
       <x:c r="I28" s="9"/>
       <x:c r="J28" s="9"/>
       <x:c r="K28" s="10" t="s">
-        <x:v>87</x:v>
+        <x:v>82</x:v>
       </x:c>
     </x:row>
     <x:row r="29" spans="1:11">
@@ -1482,66 +1464,66 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="C30" s="11" t="s">
+        <x:v>83</x:v>
+      </x:c>
+      <x:c r="D30" s="11" t="s">
+        <x:v>84</x:v>
+      </x:c>
+      <x:c r="E30" s="11" t="s">
+        <x:v>85</x:v>
+      </x:c>
+      <x:c r="F30" s="11" t="s">
+        <x:v>86</x:v>
+      </x:c>
+      <x:c r="G30" s="11" t="s">
+        <x:v>87</x:v>
+      </x:c>
+      <x:c r="H30" s="11" t="s">
         <x:v>88</x:v>
       </x:c>
-      <x:c r="D30" s="11" t="s">
+      <x:c r="I30" s="11" t="s">
         <x:v>89</x:v>
       </x:c>
-      <x:c r="E30" s="11" t="s">
+      <x:c r="J30" s="11" t="s">
         <x:v>90</x:v>
       </x:c>
-      <x:c r="F30" s="11" t="s">
+      <x:c r="K30" s="11" t="s">
         <x:v>91</x:v>
-      </x:c>
-      <x:c r="G30" s="11" t="s">
-        <x:v>92</x:v>
-      </x:c>
-      <x:c r="H30" s="11" t="s">
-        <x:v>93</x:v>
-      </x:c>
-      <x:c r="I30" s="11" t="s">
-        <x:v>94</x:v>
-      </x:c>
-      <x:c r="J30" s="11" t="s">
-        <x:v>95</x:v>
-      </x:c>
-      <x:c r="K30" s="11" t="s">
-        <x:v>96</x:v>
       </x:c>
     </x:row>
     <x:row r="31" spans="1:11" ht="30" customHeight="1">
       <x:c r="A31" s="13" t="s">
-        <x:v>97</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="B31" s="13" t="s">
-        <x:v>98</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="C31" s="13" t="s">
-        <x:v>98</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="D31" s="13" t="s">
-        <x:v>98</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="E31" s="13" t="s">
-        <x:v>98</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="F31" s="13" t="s">
-        <x:v>98</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="G31" s="13" t="s">
-        <x:v>99</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="H31" s="13" t="s">
-        <x:v>99</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="I31" s="13" t="s">
-        <x:v>98</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="J31" s="13" t="s">
-        <x:v>98</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="K31" s="13" t="s">
-        <x:v>98</x:v>
+        <x:v>93</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/data/positions/Posição Consolidada - 7983962.xlsx
+++ b/data/positions/Posição Consolidada - 7983962.xlsx
@@ -19,7 +19,7 @@
     <x:t>XP</x:t>
   </x:si>
   <x:si>
-    <x:t>Conta: 7983962 | 27/10/2026, 19:00</x:t>
+    <x:t>Conta: 7983962 | 29/10/2026, 16:10</x:t>
   </x:si>
   <x:si>
     <x:t>Este é o seu patrimônio</x:t>
@@ -37,7 +37,7 @@
     <x:t>20,7%|Renda Fixa</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 2.257.036,17</x:t>
+    <x:t>R$ 2.258.986,09</x:t>
   </x:si>
   <x:si>
     <x:t>20,60%|Pós-Fixada</x:t>
@@ -94,7 +94,7 @@
     <x:t>R$ 1.000.949,68</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 1.051.478,04</x:t>
+    <x:t>R$ 1.052.380,74</x:t>
   </x:si>
   <x:si>
     <x:t>LCI CEF - MAI/2027</x:t>
@@ -118,13 +118,13 @@
     <x:t>R$ 1.191.509,24</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 1.205.558,13</x:t>
-  </x:si>
-  <x:si>
-    <x:t>25,2%|Operações Compromissadas</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 2.744.137,74</x:t>
+    <x:t>R$ 1.206.605,35</x:t>
+  </x:si>
+  <x:si>
+    <x:t>25,1%|Operações Compromissadas</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 2.746.507,91</x:t>
   </x:si>
   <x:si>
     <x:t>25,10%|Pós-Fixada</x:t>
@@ -145,10 +145,10 @@
     <x:t>R$ 1.499.999,99</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 1.507.137,74</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 1.505.531,75</x:t>
+    <x:t>R$ 1.508.439,66</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 1.506.540,73</x:t>
   </x:si>
   <x:si>
     <x:t>27/10/2026</x:t>
@@ -163,10 +163,16 @@
     <x:t>R$ 1.237.000,00</x:t>
   </x:si>
   <x:si>
+    <x:t>R$ 1.238.068,25</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 1.237.827,89</x:t>
+  </x:si>
+  <x:si>
     <x:t>54,2%|Fundos de Investimento</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 5.909.245,53</x:t>
+    <x:t>R$ 5.915.038,42</x:t>
   </x:si>
   <x:si>
     <x:t>54,10%|Fundos de Renda Fixa Pós-Fixado</x:t>
@@ -187,6 +193,9 @@
     <x:t>XP Bancos FIRF Referenciada DI CP RL</x:t>
   </x:si>
   <x:si>
+    <x:t>29/10/2026</x:t>
+  </x:si>
+  <x:si>
     <x:t>R$ 1,97</x:t>
   </x:si>
   <x:si>
@@ -196,10 +205,10 @@
     <x:t>R$ 0,00</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 1.523.330,26</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 1.518.080,95</x:t>
+    <x:t>R$ 1.524.859,26</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 1.519.265,93</x:t>
   </x:si>
   <x:si>
     <x:t>XP Bancos FIC de FIRF Referenciado DI CP - RL</x:t>
@@ -211,25 +220,25 @@
     <x:t>526.379,08</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 819.062,82</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 816.573,69</x:t>
+    <x:t>R$ 819.867,68</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 817.197,45</x:t>
   </x:si>
   <x:si>
     <x:t>Bradesco SKY FIC FIRF Referenciada DI RL</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 1.472,21</x:t>
+    <x:t>R$ 1.473,65</x:t>
   </x:si>
   <x:si>
     <x:t>1.188,48</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 1.749.679,25</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 1.743.307,88</x:t>
+    <x:t>R$ 1.751.397,20</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 1.744.639,29</x:t>
   </x:si>
   <x:si>
     <x:t>Bradesco Bancos II FIF CIC RF CP RL</x:t>
@@ -241,25 +250,25 @@
     <x:t>353.356,60</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 531.914,65</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 524.929,56</x:t>
+    <x:t>R$ 532.459,70</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 525.351,97</x:t>
   </x:si>
   <x:si>
     <x:t>Safra Extra Bancos Special FIC FIRF CP</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 144,44</x:t>
+    <x:t>R$ 144,57</x:t>
   </x:si>
   <x:si>
     <x:t>8.898,52</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 1.285.258,55</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 1.272.419,89</x:t>
+    <x:t>R$ 1.286.454,58</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 1.273.346,81</x:t>
   </x:si>
   <x:si>
     <x:t>R$ 350,85</x:t>
@@ -900,10 +909,10 @@
     </x:row>
     <x:row r="4" spans="1:11" ht="30" customHeight="1">
       <x:c r="A4" s="6">
-        <x:v>10910770.2914802</x:v>
+        <x:v>10920883.2748447</x:v>
       </x:c>
       <x:c r="B4" s="7">
-        <x:v>10910419.4414802</x:v>
+        <x:v>10920532.4248447</x:v>
       </x:c>
       <x:c r="C4" s="7">
         <x:v>350.85</x:v>
@@ -1201,10 +1210,10 @@
         <x:v>48</x:v>
       </x:c>
       <x:c r="I17" s="13" t="s">
-        <x:v>48</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="J17" s="13" t="s">
-        <x:v>48</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="K17" s="3"/>
     </x:row>
@@ -1223,7 +1232,7 @@
     </x:row>
     <x:row r="19" spans="1:11" ht="45" customHeight="1">
       <x:c r="A19" s="8" t="s">
-        <x:v>49</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="B19" s="9"/>
       <x:c r="C19" s="9"/>
@@ -1231,7 +1240,7 @@
       <x:c r="E19" s="9"/>
       <x:c r="F19" s="9"/>
       <x:c r="G19" s="10" t="s">
-        <x:v>50</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="H19" s="3"/>
       <x:c r="I19" s="3"/>
@@ -1253,19 +1262,19 @@
     </x:row>
     <x:row r="21" spans="1:11" ht="35.1" customHeight="1">
       <x:c r="A21" s="11" t="s">
-        <x:v>51</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="B21" s="11" t="s">
-        <x:v>52</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="C21" s="11" t="s">
-        <x:v>53</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="D21" s="11" t="s">
-        <x:v>54</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="E21" s="11" t="s">
-        <x:v>55</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="F21" s="11" t="s">
         <x:v>16</x:v>
@@ -1280,25 +1289,25 @@
     </x:row>
     <x:row r="22" spans="1:11" ht="30" customHeight="1">
       <x:c r="A22" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="B22" s="12" t="s">
-        <x:v>45</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="C22" s="12" t="s">
-        <x:v>57</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="D22" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="E22" s="12" t="s">
-        <x:v>59</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="F22" s="12" t="s">
-        <x:v>60</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="G22" s="12" t="s">
-        <x:v>61</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="H22" s="3"/>
       <x:c r="I22" s="3"/>
@@ -1307,25 +1316,25 @@
     </x:row>
     <x:row r="23" spans="1:11" ht="30" customHeight="1">
       <x:c r="A23" s="12" t="s">
+        <x:v>65</x:v>
+      </x:c>
+      <x:c r="B23" s="12" t="s">
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="C23" s="12" t="s">
+        <x:v>66</x:v>
+      </x:c>
+      <x:c r="D23" s="12" t="s">
+        <x:v>67</x:v>
+      </x:c>
+      <x:c r="E23" s="12" t="s">
         <x:v>62</x:v>
       </x:c>
-      <x:c r="B23" s="12" t="s">
-        <x:v>45</x:v>
-      </x:c>
-      <x:c r="C23" s="12" t="s">
-        <x:v>63</x:v>
-      </x:c>
-      <x:c r="D23" s="12" t="s">
-        <x:v>64</x:v>
-      </x:c>
-      <x:c r="E23" s="12" t="s">
-        <x:v>59</x:v>
-      </x:c>
       <x:c r="F23" s="12" t="s">
-        <x:v>65</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="G23" s="12" t="s">
-        <x:v>66</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="H23" s="3"/>
       <x:c r="I23" s="3"/>
@@ -1334,25 +1343,25 @@
     </x:row>
     <x:row r="24" spans="1:11" ht="30" customHeight="1">
       <x:c r="A24" s="12" t="s">
-        <x:v>67</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="B24" s="12" t="s">
-        <x:v>45</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="C24" s="12" t="s">
-        <x:v>68</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="D24" s="12" t="s">
-        <x:v>69</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="E24" s="12" t="s">
-        <x:v>59</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="F24" s="12" t="s">
-        <x:v>70</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="G24" s="12" t="s">
-        <x:v>71</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="H24" s="3"/>
       <x:c r="I24" s="3"/>
@@ -1361,25 +1370,25 @@
     </x:row>
     <x:row r="25" spans="1:11" ht="30" customHeight="1">
       <x:c r="A25" s="12" t="s">
-        <x:v>72</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="B25" s="12" t="s">
-        <x:v>45</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="C25" s="12" t="s">
-        <x:v>73</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="D25" s="12" t="s">
-        <x:v>74</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="E25" s="12" t="s">
-        <x:v>59</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="F25" s="12" t="s">
-        <x:v>75</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="G25" s="12" t="s">
-        <x:v>76</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="H25" s="3"/>
       <x:c r="I25" s="3"/>
@@ -1388,25 +1397,25 @@
     </x:row>
     <x:row r="26" spans="1:11" ht="30" customHeight="1">
       <x:c r="A26" s="13" t="s">
-        <x:v>77</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="B26" s="13" t="s">
-        <x:v>45</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="C26" s="13" t="s">
-        <x:v>78</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="D26" s="13" t="s">
-        <x:v>79</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="E26" s="13" t="s">
-        <x:v>59</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="F26" s="13" t="s">
-        <x:v>80</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="G26" s="13" t="s">
-        <x:v>81</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="H26" s="3"/>
       <x:c r="I26" s="3"/>
@@ -1440,7 +1449,7 @@
       <x:c r="I28" s="9"/>
       <x:c r="J28" s="9"/>
       <x:c r="K28" s="10" t="s">
-        <x:v>82</x:v>
+        <x:v>85</x:v>
       </x:c>
     </x:row>
     <x:row r="29" spans="1:11">
@@ -1464,66 +1473,66 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="C30" s="11" t="s">
-        <x:v>83</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="D30" s="11" t="s">
-        <x:v>84</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="E30" s="11" t="s">
-        <x:v>85</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="F30" s="11" t="s">
-        <x:v>86</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="G30" s="11" t="s">
-        <x:v>87</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="H30" s="11" t="s">
-        <x:v>88</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="I30" s="11" t="s">
-        <x:v>89</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="J30" s="11" t="s">
-        <x:v>90</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="K30" s="11" t="s">
-        <x:v>91</x:v>
+        <x:v>94</x:v>
       </x:c>
     </x:row>
     <x:row r="31" spans="1:11" ht="30" customHeight="1">
       <x:c r="A31" s="13" t="s">
-        <x:v>92</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="B31" s="13" t="s">
-        <x:v>93</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="C31" s="13" t="s">
-        <x:v>93</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="D31" s="13" t="s">
-        <x:v>93</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="E31" s="13" t="s">
-        <x:v>93</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="F31" s="13" t="s">
-        <x:v>93</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="G31" s="13" t="s">
-        <x:v>93</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="H31" s="13" t="s">
-        <x:v>93</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="I31" s="13" t="s">
-        <x:v>93</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="J31" s="13" t="s">
-        <x:v>93</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="K31" s="13" t="s">
-        <x:v>93</x:v>
+        <x:v>96</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
